--- a/single-api/services/rule-api/swagger_modules.xlsx
+++ b/single-api/services/rule-api/swagger_modules.xlsx
@@ -676,9 +676,19 @@
         <v>2</v>
       </c>
       <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
+      <c r="F6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>100% (2/2)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n"/>
@@ -696,9 +706,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
+      <c r="F7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>100% (1/1)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
@@ -1306,9 +1326,19 @@
         <v>2</v>
       </c>
       <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n"/>
-      <c r="H30" s="3" t="n"/>
+      <c r="F30" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>100% (2/2)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n"/>
@@ -1326,9 +1356,19 @@
         <v>1</v>
       </c>
       <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
+      <c r="F31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>100% (1/1)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n"/>
@@ -5929,11 +5969,11 @@
       <c r="F64" s="3" t="n"/>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>walmart平台月度功能使用报告 — 2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="16" customHeight="1">
+          <t>场景1: amazon平台月度功能使用报告</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="32" customHeight="1">
       <c r="A65" s="3" t="n"/>
       <c r="B65" s="3" t="inlineStr">
         <is>
@@ -5958,7 +5998,8 @@
       <c r="F65" s="3" t="n"/>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>amazon平台Top N客户功能使用排行 — 2%</t>
+          <t>场景1: amazon平台eventType=Data Impact
+场景2: amazon平台eventType=Profitero</t>
         </is>
       </c>
     </row>
@@ -5987,7 +6028,7 @@
       <c r="F66" s="3" t="n"/>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>服务健康检查（无ES流量）</t>
+          <t>场景1: 服务健康检查</t>
         </is>
       </c>
     </row>
@@ -14322,11 +14363,11 @@
       <c r="F360" s="3" t="n"/>
       <c r="G360" s="7" t="inlineStr">
         <is>
-          <t>walmart平台月度功能使用报告 — 2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="361" ht="16" customHeight="1">
+          <t>场景1: walmart平台月度功能使用报告</t>
+        </is>
+      </c>
+    </row>
+    <row r="361" ht="32" customHeight="1">
       <c r="A361" s="3" t="n"/>
       <c r="B361" s="3" t="inlineStr">
         <is>
@@ -14351,7 +14392,8 @@
       <c r="F361" s="3" t="n"/>
       <c r="G361" s="7" t="inlineStr">
         <is>
-          <t>amazon平台Top N客户功能使用排行 — 2%</t>
+          <t>场景1: walmart平台eventType=Data Impact
+场景2: walmart平台eventType=Profitero</t>
         </is>
       </c>
     </row>
@@ -14380,7 +14422,7 @@
       <c r="F362" s="3" t="n"/>
       <c r="G362" s="7" t="inlineStr">
         <is>
-          <t>服务健康检查（无ES流量）</t>
+          <t>场景1: 服务健康检查</t>
         </is>
       </c>
     </row>

--- a/single-api/services/rule-api/swagger_modules.xlsx
+++ b/single-api/services/rule-api/swagger_modules.xlsx
@@ -736,9 +736,19 @@
         <v>26</v>
       </c>
       <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
+      <c r="F8" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>100% (26/26)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n"/>
@@ -776,9 +786,19 @@
         <v>13</v>
       </c>
       <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
+      <c r="F10" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>85% (11/13)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
@@ -796,9 +816,19 @@
         <v>9</v>
       </c>
       <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
+      <c r="F11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>100% (9/9)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n"/>
@@ -816,9 +846,19 @@
         <v>22</v>
       </c>
       <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
+      <c r="F12" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>73% (16/22)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n"/>
@@ -836,9 +876,19 @@
         <v>5</v>
       </c>
       <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
+      <c r="F13" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>80% (4/5)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
@@ -1386,9 +1436,19 @@
         <v>26</v>
       </c>
       <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n"/>
-      <c r="G32" s="3" t="n"/>
-      <c r="H32" s="3" t="n"/>
+      <c r="F32" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>100% (26/26)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n"/>
@@ -1426,9 +1486,19 @@
         <v>13</v>
       </c>
       <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="n"/>
+      <c r="F34" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>85% (11/13)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n"/>
@@ -1446,9 +1516,19 @@
         <v>9</v>
       </c>
       <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n"/>
-      <c r="G35" s="3" t="n"/>
-      <c r="H35" s="3" t="n"/>
+      <c r="F35" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>100% (9/9)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n"/>
@@ -1466,9 +1546,19 @@
         <v>22</v>
       </c>
       <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="n"/>
-      <c r="G36" s="3" t="n"/>
-      <c r="H36" s="3" t="n"/>
+      <c r="F36" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>73% (16/22)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n"/>
@@ -1486,9 +1576,19 @@
         <v>5</v>
       </c>
       <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n"/>
-      <c r="G37" s="3" t="n"/>
-      <c r="H37" s="3" t="n"/>
+      <c r="F37" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>80% (4/5)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n"/>
@@ -6057,7 +6157,7 @@
       <c r="F67" s="3" t="n"/>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>变更建议操作状态[需实际建议记录]（无ES流量）</t>
+          <t>场景1: 变更建议操作状态</t>
         </is>
       </c>
     </row>
@@ -6086,7 +6186,7 @@
       <c r="F68" s="3" t="n"/>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>执行日志AdGroup列表（无ES流量）</t>
+          <t>场景1: 执行日志AdGroup列表</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6215,7 @@
       <c r="F69" s="3" t="n"/>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>Adtomic建议操作列表（无ES流量）</t>
+          <t>场景1: Adtomic建议操作列表</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6244,7 @@
       <c r="F70" s="3" t="n"/>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>自动规则详情日志[Amazon专属]（无ES流量）</t>
+          <t>场景1: 自动规则详情日志(Amazon专属)[FAIL]</t>
         </is>
       </c>
     </row>
@@ -6173,7 +6273,7 @@
       <c r="F71" s="3" t="n"/>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>自动规则日志过滤器[Amazon专属]（无ES流量）</t>
+          <t>场景1: 自动规则日志过滤器(Amazon专属)[FAIL]</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6302,7 @@
       <c r="F72" s="3" t="n"/>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>自动规则执行日志列表[Amazon专属]（无ES流量）</t>
+          <t>场景1: 自动规则执行日志列表(Amazon专属)</t>
         </is>
       </c>
     </row>
@@ -6231,7 +6331,7 @@
       <c r="F73" s="3" t="n"/>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>执行日志Campaign列表 — 100%</t>
+          <t>场景1: 执行日志Campaign列表</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6360,7 @@
       <c r="F74" s="3" t="n"/>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>执行日志CampaignTag列表 — 100%</t>
+          <t>场景1: 执行日志CampaignTag列表</t>
         </is>
       </c>
     </row>
@@ -6289,7 +6389,7 @@
       <c r="F75" s="3" t="n"/>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>执行日志详情[需TikTok执行历史]（无ES流量）</t>
+          <t>场景1: 执行日志详情</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6418,7 @@
       <c r="F76" s="3" t="n"/>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>历史执行记录列表 — 100%</t>
+          <t>场景1: 历史执行记录列表</t>
         </is>
       </c>
     </row>
@@ -6347,7 +6447,7 @@
       <c r="F77" s="3" t="n"/>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>执行日志LineItem列表（无ES流量）</t>
+          <t>场景1: 执行日志LineItem列表</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6476,7 @@
       <c r="F78" s="3" t="n"/>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>待处理规则列表 — 100%</t>
+          <t>场景1: 待处理规则列表</t>
         </is>
       </c>
     </row>
@@ -6405,7 +6505,7 @@
       <c r="F79" s="3" t="n"/>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>待处理规则数量 — 100%</t>
+          <t>场景1: 待处理规则数量</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6534,7 @@
       <c r="F80" s="3" t="n"/>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>执行日志Product列表（无ES流量）</t>
+          <t>场景1: 执行日志Product列表</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6563,7 @@
       <c r="F81" s="3" t="n"/>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>执行日志Profile列表 — 100%</t>
+          <t>场景1: 执行日志Profile列表</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6592,7 @@
       <c r="F82" s="3" t="n"/>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>归档旧日志（运维接口）（无ES流量）</t>
+          <t>场景1: 归档旧日志（运维接口）</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6650,7 @@
       <c r="F84" s="3" t="n"/>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>导出执行日志[需TikTok执行历史]（无ES流量）</t>
+          <t>场景1: 导出执行日志</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6679,7 @@
       <c r="F85" s="3" t="n"/>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>规则最近暂停ASIN列表（无ES流量）</t>
+          <t>场景1: 规则最近暂停ASIN列表</t>
         </is>
       </c>
     </row>
@@ -6608,7 +6708,7 @@
       <c r="F86" s="3" t="n"/>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>标准告警计数查询 — 100%</t>
+          <t>场景1: 标准告警计数查询</t>
         </is>
       </c>
     </row>
@@ -6637,7 +6737,7 @@
       <c r="F87" s="3" t="n"/>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>规则告警详情列表 — 100%</t>
+          <t>场景1: 规则告警详情列表</t>
         </is>
       </c>
     </row>
@@ -6666,7 +6766,7 @@
       <c r="F88" s="3" t="n"/>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>规则失效详情（无ES流量）</t>
+          <t>场景1: 规则失效详情</t>
         </is>
       </c>
     </row>
@@ -6695,7 +6795,7 @@
       <c r="F89" s="3" t="n"/>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>导出待处理列表[需TikTok执行历史]（无ES流量）</t>
+          <t>场景1: 导出待处理列表</t>
         </is>
       </c>
     </row>
@@ -6724,7 +6824,7 @@
       <c r="F90" s="3" t="n"/>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>规则快照查询 — 100%</t>
+          <t>场景1: 按测试账号真实规则查询快照</t>
         </is>
       </c>
     </row>
@@ -6753,7 +6853,7 @@
       <c r="F91" s="3" t="n"/>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>设置忽略操作[需TikTok执行历史]（无ES流量）</t>
+          <t>场景1: 设置忽略操作</t>
         </is>
       </c>
     </row>
@@ -6782,7 +6882,7 @@
       <c r="F92" s="3" t="n"/>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>设置执行日志备注[需TikTok执行历史]（无ES流量）</t>
+          <t>场景1: 设置执行日志备注</t>
         </is>
       </c>
     </row>
@@ -6898,7 +6998,7 @@
       <c r="F96" s="3" t="n"/>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>获取Profitero国家列表 — 52%</t>
+          <t>场景1: 默认调用(无入参) / 查询Profitero国家列表</t>
         </is>
       </c>
     </row>
@@ -6927,7 +7027,7 @@
       <c r="F97" s="3" t="n"/>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>walmart平台品牌事件列表 — 12%</t>
+          <t>场景1: 默认查询 / 查询品牌事件列表</t>
         </is>
       </c>
     </row>
@@ -6956,7 +7056,7 @@
       <c r="F98" s="3" t="n"/>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>walmart平台竞争品牌汇总</t>
+          <t>场景1: 默认查询 / 查询竞品品牌汇总</t>
         </is>
       </c>
     </row>
@@ -6985,7 +7085,7 @@
       <c r="F99" s="3" t="n"/>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>target平台执行记录汇总 — 12%</t>
+          <t>场景1: 默认查询 / 查询执行记录汇总</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7114,7 @@
       <c r="F100" s="3" t="n"/>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>walmart平台获取所有品牌</t>
+          <t>场景1: 默认查询 / 查询全部品牌</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7143,7 @@
       <c r="F101" s="3" t="n"/>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>获取所有Profitero规则</t>
+          <t>场景1: 默认查询 / 查询全部Profitero规则</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7172,7 @@
       <c r="F102" s="3" t="n"/>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>查询Profitero规则应用记录 — 7%</t>
+          <t>场景1: 默认查询 / 查询Profitero规则应用情况</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7201,7 @@
       <c r="F103" s="3" t="n"/>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>walmart平台获取ASIN列表 — 12%</t>
+          <t>场景1: 默认查询 / 查询ASIN列表</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7230,7 @@
       <c r="F104" s="3" t="n"/>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>查询每日规则数据</t>
+          <t>场景1: 默认查询 / 查询规则每日数据</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7259,7 @@
       <c r="F105" s="3" t="n"/>
       <c r="G105" s="7" t="inlineStr">
         <is>
-          <t>amazon平台获取信号数据 — 12%</t>
+          <t>场景1: 默认查询 / 查询信号列表</t>
         </is>
       </c>
     </row>
@@ -7188,7 +7288,7 @@
       <c r="F106" s="3" t="n"/>
       <c r="G106" s="7" t="inlineStr">
         <is>
-          <t>target平台我的品牌数量汇总 — 6%</t>
+          <t>场景1: 默认查询 / 查询我的品牌数量汇总</t>
         </is>
       </c>
     </row>
@@ -7275,7 +7375,7 @@
       <c r="F109" s="3" t="n"/>
       <c r="G109" s="7" t="inlineStr">
         <is>
-          <t>校验共享通行证有效性 — 12%</t>
+          <t>场景1: amazon / check SharePass</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7404,7 @@
       <c r="F110" s="3" t="n"/>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>创建共享通行证后删除（可重复） — 8%</t>
+          <t>场景1: amazon / 创建SharePass</t>
         </is>
       </c>
     </row>
@@ -7333,11 +7433,11 @@
       <c r="F111" s="3" t="n"/>
       <c r="G111" s="7" t="inlineStr">
         <is>
-          <t>获取创建者列表 — 23%</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
+          <t>场景1: 默认调用(无入参) / 查询创建者列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="16" customHeight="1">
       <c r="A112" s="3" t="n"/>
       <c r="B112" s="3" t="inlineStr">
         <is>
@@ -7360,7 +7460,11 @@
         </is>
       </c>
       <c r="F112" s="3" t="n"/>
-      <c r="G112" s="3" t="n"/>
+      <c r="G112" s="7" t="inlineStr">
+        <is>
+          <t>场景1: amazon / 清理-删除SharePass</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="16" customHeight="1">
       <c r="A113" s="3" t="n"/>
@@ -7387,7 +7491,7 @@
       <c r="F113" s="3" t="n"/>
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>编辑共享通行证（无ES流量）</t>
+          <t>场景1: amazon / 编辑SharePass状态</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7520,7 @@
       <c r="F114" s="3" t="n"/>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>获取可共享账户列表 — 25%</t>
+          <t>场景1: 默认调用(无入参) / 查询账号列表</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7549,7 @@
       <c r="F115" s="3" t="n"/>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>通过共享通行证获取规则ID列表</t>
+          <t>场景1: amazon / 查询SharePass关联规则ID</t>
         </is>
       </c>
     </row>
@@ -7474,7 +7578,7 @@
       <c r="F116" s="3" t="n"/>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>获取可共享平台列表 — 8%</t>
+          <t>场景1: 默认查询 / 查询可分享平台列表</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7607,7 @@
       <c r="F117" s="3" t="n"/>
       <c r="G117" s="7" t="inlineStr">
         <is>
-          <t>amazon平台分页查询共享通行证列表 — 24%</t>
+          <t>场景1: 默认查询 / 查询SharePass列表</t>
         </is>
       </c>
     </row>
@@ -7532,11 +7636,11 @@
       <c r="F118" s="3" t="n"/>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>创建模板并批量创建(可重复)</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="16" customHeight="1">
+          <t>场景1: amazon / 创建模板</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="32" customHeight="1">
       <c r="A119" s="3" t="n"/>
       <c r="B119" s="3" t="inlineStr">
         <is>
@@ -7561,7 +7665,8 @@
       <c r="F119" s="3" t="n"/>
       <c r="G119" s="7" t="inlineStr">
         <is>
-          <t>删除模板（需有效templateId）</t>
+          <t>场景1: amazon / 清理-删除模板
+场景2: amazon / 清理-删除bulk创建的模板</t>
         </is>
       </c>
     </row>
@@ -7590,11 +7695,11 @@
       <c r="F120" s="3" t="n"/>
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>模板收藏切换</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
+          <t>场景1: amazon / 收藏模板</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="16" customHeight="1">
       <c r="A121" s="3" t="n"/>
       <c r="B121" s="3" t="inlineStr">
         <is>
@@ -7617,7 +7722,11 @@
         </is>
       </c>
       <c r="F121" s="3" t="n"/>
-      <c r="G121" s="3" t="n"/>
+      <c r="G121" s="7" t="inlineStr">
+        <is>
+          <t>场景1: amazon / 批量创建模板</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="16" customHeight="1">
       <c r="A122" s="3" t="n"/>
@@ -7644,11 +7753,11 @@
       <c r="F122" s="3" t="n"/>
       <c r="G122" s="7" t="inlineStr">
         <is>
-          <t>创建编辑删除分类(可重复)</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
+          <t>场景1: amazon / 创建分类</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="16" customHeight="1">
       <c r="A123" s="3" t="n"/>
       <c r="B123" s="3" t="inlineStr">
         <is>
@@ -7671,7 +7780,11 @@
         </is>
       </c>
       <c r="F123" s="3" t="n"/>
-      <c r="G123" s="3" t="n"/>
+      <c r="G123" s="7" t="inlineStr">
+        <is>
+          <t>场景1: amazon / 清理-删除分类</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="16" customHeight="1">
       <c r="A124" s="3" t="n"/>
@@ -7727,7 +7840,7 @@
       <c r="F125" s="3" t="n"/>
       <c r="G125" s="3" t="n"/>
     </row>
-    <row r="126">
+    <row r="126" ht="16" customHeight="1">
       <c r="A126" s="3" t="n"/>
       <c r="B126" s="3" t="inlineStr">
         <is>
@@ -7750,7 +7863,11 @@
         </is>
       </c>
       <c r="F126" s="3" t="n"/>
-      <c r="G126" s="3" t="n"/>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>场景1: amazon / 编辑分类</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n"/>
@@ -7831,7 +7948,7 @@
       <c r="F129" s="3" t="n"/>
       <c r="G129" s="7" t="inlineStr">
         <is>
-          <t>创建模板并验证editTemplate端点可达(可重复)</t>
+          <t>场景1: amazon / 编辑模板</t>
         </is>
       </c>
     </row>
@@ -7860,8 +7977,8 @@
       <c r="F130" s="3" t="n"/>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>无ruleType过滤查询全部分类 — 40%
-Targeting类型模板分类 — 40%</t>
+          <t>场景1: 默认查询 / 查询分类列表
+场景2: amazon / 查询新建分类的ID</t>
         </is>
       </c>
     </row>
@@ -7890,7 +8007,7 @@
       <c r="F131" s="3" t="n"/>
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>获取默认模板分类 — 0.11%</t>
+          <t>场景1: 默认查询 / 查询默认分类列表</t>
         </is>
       </c>
     </row>
@@ -7919,7 +8036,7 @@
       <c r="F132" s="3" t="n"/>
       <c r="G132" s="7" t="inlineStr">
         <is>
-          <t>获取默认模板列表 — 0.15%</t>
+          <t>场景1: 默认查询 / 查询默认模板列表</t>
         </is>
       </c>
     </row>
@@ -7948,11 +8065,11 @@
       <c r="F133" s="3" t="n"/>
       <c r="G133" s="7" t="inlineStr">
         <is>
-          <t>获取模板创建者列表 — 3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
+          <t>场景1: 默认调用(无入参) / 查询模板所有者列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="16" customHeight="1">
       <c r="A134" s="3" t="n"/>
       <c r="B134" s="3" t="inlineStr">
         <is>
@@ -7975,9 +8092,13 @@
         </is>
       </c>
       <c r="F134" s="3" t="n"/>
-      <c r="G134" s="3" t="n"/>
-    </row>
-    <row r="135" ht="16" customHeight="1">
+      <c r="G134" s="7" t="inlineStr">
+        <is>
+          <t>场景1: 默认查询 / 查询推荐模板</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="48" customHeight="1">
       <c r="A135" s="3" t="n"/>
       <c r="B135" s="3" t="inlineStr">
         <is>
@@ -8002,7 +8123,9 @@
       <c r="F135" s="3" t="n"/>
       <c r="G135" s="7" t="inlineStr">
         <is>
-          <t>onlyFavorite:true查询收藏模板 — 47%</t>
+          <t>场景1: 按ruleType筛选 / 按ruleType查询模板列表
+场景2: amazon / 查询新建模板的ID
+场景3: amazon / 查询bulk新建模板的ID</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8154,7 @@
       <c r="F136" s="3" t="n"/>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>通过直链分享获取模板列表</t>
+          <t>场景1: 测试账号真实模板 / 查询DirectShare模板列表</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8241,7 @@
       <c r="F139" s="3" t="n"/>
       <c r="G139" s="7" t="inlineStr">
         <is>
-          <t>移动模板到分类(创建临时分类,可重复)</t>
+          <t>场景1: amazon / 移动模板到另一分类</t>
         </is>
       </c>
     </row>
@@ -8176,7 +8299,7 @@
       <c r="F141" s="3" t="n"/>
       <c r="G141" s="7" t="inlineStr">
         <is>
-          <t>按campaignId统计规则数量(无ES流量,TikTok返回405)（无ES流量）</t>
+          <t>场景1: 测试账号真实campaign / 按CampaignId查询规则数量</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8328,7 @@
       <c r="F142" s="3" t="n"/>
       <c r="G142" s="7" t="inlineStr">
         <is>
-          <t>按userId统计TikTok规则数量 — 100%</t>
+          <t>场景1: 测试账号真实user / 按UserId查询规则数量</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8357,7 @@
       <c r="F143" s="3" t="n"/>
       <c r="G143" s="7" t="inlineStr">
         <is>
-          <t>按ruleIds批量获取规则定义(创建临时规则,可重复) — 100%</t>
+          <t>场景1: 测试账号真实规则 / 查询规则定义</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8386,7 @@
       <c r="F144" s="3" t="n"/>
       <c r="G144" s="7" t="inlineStr">
         <is>
-          <t>获取规则类型列表 — 100%</t>
+          <t>场景1: 默认调用(无入参) / 查询规则类型列表</t>
         </is>
       </c>
     </row>
@@ -14451,7 +14574,7 @@
       <c r="F363" s="3" t="n"/>
       <c r="G363" s="7" t="inlineStr">
         <is>
-          <t>变更建议操作状态[需实际建议记录]（无ES流量）</t>
+          <t>场景1: 变更建议操作状态</t>
         </is>
       </c>
     </row>
@@ -14480,7 +14603,7 @@
       <c r="F364" s="3" t="n"/>
       <c r="G364" s="7" t="inlineStr">
         <is>
-          <t>执行日志AdGroup列表（无ES流量）</t>
+          <t>场景1: 执行日志AdGroup列表</t>
         </is>
       </c>
     </row>
@@ -14509,7 +14632,7 @@
       <c r="F365" s="3" t="n"/>
       <c r="G365" s="7" t="inlineStr">
         <is>
-          <t>Adtomic建议操作列表（无ES流量）</t>
+          <t>场景1: Adtomic建议操作列表</t>
         </is>
       </c>
     </row>
@@ -14538,7 +14661,7 @@
       <c r="F366" s="3" t="n"/>
       <c r="G366" s="7" t="inlineStr">
         <is>
-          <t>自动规则详情日志[Amazon专属]（无ES流量）</t>
+          <t>场景1: Amazon专属，walmart预期不支持[FAIL]</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14690,7 @@
       <c r="F367" s="3" t="n"/>
       <c r="G367" s="7" t="inlineStr">
         <is>
-          <t>自动规则日志过滤器[Amazon专属]（无ES流量）</t>
+          <t>场景1: Amazon专属，walmart预期不支持[FAIL]</t>
         </is>
       </c>
     </row>
@@ -14596,7 +14719,7 @@
       <c r="F368" s="3" t="n"/>
       <c r="G368" s="7" t="inlineStr">
         <is>
-          <t>自动规则执行日志列表[Amazon专属]（无ES流量）</t>
+          <t>场景1: Amazon专属，walmart预期不支持</t>
         </is>
       </c>
     </row>
@@ -14625,7 +14748,7 @@
       <c r="F369" s="3" t="n"/>
       <c r="G369" s="7" t="inlineStr">
         <is>
-          <t>执行日志Campaign列表 — 100%</t>
+          <t>场景1: 执行日志Campaign列表</t>
         </is>
       </c>
     </row>
@@ -14654,7 +14777,7 @@
       <c r="F370" s="3" t="n"/>
       <c r="G370" s="7" t="inlineStr">
         <is>
-          <t>执行日志CampaignTag列表 — 100%</t>
+          <t>场景1: 执行日志CampaignTag列表</t>
         </is>
       </c>
     </row>
@@ -14683,7 +14806,7 @@
       <c r="F371" s="3" t="n"/>
       <c r="G371" s="7" t="inlineStr">
         <is>
-          <t>执行日志详情[需TikTok执行历史]（无ES流量）</t>
+          <t>场景1: 执行日志详情</t>
         </is>
       </c>
     </row>
@@ -14712,7 +14835,7 @@
       <c r="F372" s="3" t="n"/>
       <c r="G372" s="7" t="inlineStr">
         <is>
-          <t>历史执行记录列表 — 100%</t>
+          <t>场景1: 历史执行记录列表</t>
         </is>
       </c>
     </row>
@@ -14741,7 +14864,7 @@
       <c r="F373" s="3" t="n"/>
       <c r="G373" s="7" t="inlineStr">
         <is>
-          <t>执行日志LineItem列表（无ES流量）</t>
+          <t>场景1: 执行日志LineItem列表</t>
         </is>
       </c>
     </row>
@@ -14770,7 +14893,7 @@
       <c r="F374" s="3" t="n"/>
       <c r="G374" s="7" t="inlineStr">
         <is>
-          <t>待处理规则列表 — 100%</t>
+          <t>场景1: 待处理规则列表</t>
         </is>
       </c>
     </row>
@@ -14799,7 +14922,7 @@
       <c r="F375" s="3" t="n"/>
       <c r="G375" s="7" t="inlineStr">
         <is>
-          <t>待处理规则数量 — 100%</t>
+          <t>场景1: 待处理规则数量</t>
         </is>
       </c>
     </row>
@@ -14828,7 +14951,7 @@
       <c r="F376" s="3" t="n"/>
       <c r="G376" s="7" t="inlineStr">
         <is>
-          <t>执行日志Product列表（无ES流量）</t>
+          <t>场景1: 执行日志Product列表</t>
         </is>
       </c>
     </row>
@@ -14857,7 +14980,7 @@
       <c r="F377" s="3" t="n"/>
       <c r="G377" s="7" t="inlineStr">
         <is>
-          <t>执行日志Profile列表 — 100%</t>
+          <t>场景1: 执行日志Profile列表</t>
         </is>
       </c>
     </row>
@@ -14886,7 +15009,7 @@
       <c r="F378" s="3" t="n"/>
       <c r="G378" s="7" t="inlineStr">
         <is>
-          <t>归档旧日志（运维接口）（无ES流量）</t>
+          <t>场景1: 归档旧日志（运维接口）</t>
         </is>
       </c>
     </row>
@@ -14944,7 +15067,7 @@
       <c r="F380" s="3" t="n"/>
       <c r="G380" s="7" t="inlineStr">
         <is>
-          <t>导出执行日志[需TikTok执行历史]（无ES流量）</t>
+          <t>场景1: 导出执行日志</t>
         </is>
       </c>
     </row>
@@ -14973,7 +15096,7 @@
       <c r="F381" s="3" t="n"/>
       <c r="G381" s="7" t="inlineStr">
         <is>
-          <t>规则最近暂停ASIN列表（无ES流量）</t>
+          <t>场景1: 规则最近暂停ASIN列表</t>
         </is>
       </c>
     </row>
@@ -15002,7 +15125,7 @@
       <c r="F382" s="3" t="n"/>
       <c r="G382" s="7" t="inlineStr">
         <is>
-          <t>标准告警计数查询 — 100%</t>
+          <t>场景1: 标准告警计数查询</t>
         </is>
       </c>
     </row>
@@ -15031,7 +15154,7 @@
       <c r="F383" s="3" t="n"/>
       <c r="G383" s="7" t="inlineStr">
         <is>
-          <t>规则告警详情列表 — 100%</t>
+          <t>场景1: 规则告警详情列表</t>
         </is>
       </c>
     </row>
@@ -15060,7 +15183,7 @@
       <c r="F384" s="3" t="n"/>
       <c r="G384" s="7" t="inlineStr">
         <is>
-          <t>规则失效详情（无ES流量）</t>
+          <t>场景1: 规则失效详情</t>
         </is>
       </c>
     </row>
@@ -15089,7 +15212,7 @@
       <c r="F385" s="3" t="n"/>
       <c r="G385" s="7" t="inlineStr">
         <is>
-          <t>导出待处理列表[需TikTok执行历史]（无ES流量）</t>
+          <t>场景1: 导出待处理列表</t>
         </is>
       </c>
     </row>
@@ -15118,7 +15241,7 @@
       <c r="F386" s="3" t="n"/>
       <c r="G386" s="7" t="inlineStr">
         <is>
-          <t>规则快照查询 — 100%</t>
+          <t>场景1: walmart构造(测试账号无真实规则)</t>
         </is>
       </c>
     </row>
@@ -15147,7 +15270,7 @@
       <c r="F387" s="3" t="n"/>
       <c r="G387" s="7" t="inlineStr">
         <is>
-          <t>设置忽略操作[需TikTok执行历史]（无ES流量）</t>
+          <t>场景1: 设置忽略操作</t>
         </is>
       </c>
     </row>
@@ -15176,7 +15299,7 @@
       <c r="F388" s="3" t="n"/>
       <c r="G388" s="7" t="inlineStr">
         <is>
-          <t>设置执行日志备注[需TikTok执行历史]（无ES流量）</t>
+          <t>场景1: 设置执行日志备注</t>
         </is>
       </c>
     </row>
@@ -15292,7 +15415,7 @@
       <c r="F392" s="3" t="n"/>
       <c r="G392" s="7" t="inlineStr">
         <is>
-          <t>获取Profitero国家列表 — 52%</t>
+          <t>场景1: 默认调用(无入参) / 查询Profitero国家列表</t>
         </is>
       </c>
     </row>
@@ -15321,7 +15444,7 @@
       <c r="F393" s="3" t="n"/>
       <c r="G393" s="7" t="inlineStr">
         <is>
-          <t>walmart平台品牌事件列表 — 12%</t>
+          <t>场景1: 默认查询 / 查询品牌事件列表</t>
         </is>
       </c>
     </row>
@@ -15350,7 +15473,7 @@
       <c r="F394" s="3" t="n"/>
       <c r="G394" s="7" t="inlineStr">
         <is>
-          <t>walmart平台竞争品牌汇总</t>
+          <t>场景1: 默认查询 / 查询竞品品牌汇总</t>
         </is>
       </c>
     </row>
@@ -15379,7 +15502,7 @@
       <c r="F395" s="3" t="n"/>
       <c r="G395" s="7" t="inlineStr">
         <is>
-          <t>target平台执行记录汇总 — 12%</t>
+          <t>场景1: 默认查询 / 查询执行记录汇总</t>
         </is>
       </c>
     </row>
@@ -15408,7 +15531,7 @@
       <c r="F396" s="3" t="n"/>
       <c r="G396" s="7" t="inlineStr">
         <is>
-          <t>walmart平台获取所有品牌</t>
+          <t>场景1: 默认查询 / 查询全部品牌</t>
         </is>
       </c>
     </row>
@@ -15437,7 +15560,7 @@
       <c r="F397" s="3" t="n"/>
       <c r="G397" s="7" t="inlineStr">
         <is>
-          <t>获取所有Profitero规则</t>
+          <t>场景1: 默认查询 / 查询全部Profitero规则</t>
         </is>
       </c>
     </row>
@@ -15466,7 +15589,7 @@
       <c r="F398" s="3" t="n"/>
       <c r="G398" s="7" t="inlineStr">
         <is>
-          <t>查询Profitero规则应用记录 — 7%</t>
+          <t>场景1: 默认查询 / 查询Profitero规则应用情况</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15618,7 @@
       <c r="F399" s="3" t="n"/>
       <c r="G399" s="7" t="inlineStr">
         <is>
-          <t>walmart平台获取ASIN列表 — 12%</t>
+          <t>场景1: 默认查询 / 查询ASIN列表</t>
         </is>
       </c>
     </row>
@@ -15524,7 +15647,7 @@
       <c r="F400" s="3" t="n"/>
       <c r="G400" s="7" t="inlineStr">
         <is>
-          <t>查询每日规则数据</t>
+          <t>场景1: 默认查询 / 查询规则每日数据</t>
         </is>
       </c>
     </row>
@@ -15553,7 +15676,7 @@
       <c r="F401" s="3" t="n"/>
       <c r="G401" s="7" t="inlineStr">
         <is>
-          <t>amazon平台获取信号数据 — 12%</t>
+          <t>场景1: 默认查询 / 查询信号列表</t>
         </is>
       </c>
     </row>
@@ -15582,7 +15705,7 @@
       <c r="F402" s="3" t="n"/>
       <c r="G402" s="7" t="inlineStr">
         <is>
-          <t>target平台我的品牌数量汇总 — 6%</t>
+          <t>场景1: 默认查询 / 查询我的品牌数量汇总</t>
         </is>
       </c>
     </row>
@@ -15669,7 +15792,7 @@
       <c r="F405" s="3" t="n"/>
       <c r="G405" s="7" t="inlineStr">
         <is>
-          <t>校验共享通行证有效性 — 12%</t>
+          <t>场景1: walmart / check SharePass</t>
         </is>
       </c>
     </row>
@@ -15698,7 +15821,7 @@
       <c r="F406" s="3" t="n"/>
       <c r="G406" s="7" t="inlineStr">
         <is>
-          <t>创建共享通行证后删除（可重复） — 8%</t>
+          <t>场景1: walmart / 创建SharePass</t>
         </is>
       </c>
     </row>
@@ -15727,11 +15850,11 @@
       <c r="F407" s="3" t="n"/>
       <c r="G407" s="7" t="inlineStr">
         <is>
-          <t>获取创建者列表 — 23%</t>
-        </is>
-      </c>
-    </row>
-    <row r="408">
+          <t>场景1: 默认调用(无入参) / 查询创建者列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="408" ht="16" customHeight="1">
       <c r="A408" s="3" t="n"/>
       <c r="B408" s="3" t="inlineStr">
         <is>
@@ -15754,7 +15877,11 @@
         </is>
       </c>
       <c r="F408" s="3" t="n"/>
-      <c r="G408" s="3" t="n"/>
+      <c r="G408" s="7" t="inlineStr">
+        <is>
+          <t>场景1: walmart / 清理-删除SharePass</t>
+        </is>
+      </c>
     </row>
     <row r="409" ht="16" customHeight="1">
       <c r="A409" s="3" t="n"/>
@@ -15781,7 +15908,7 @@
       <c r="F409" s="3" t="n"/>
       <c r="G409" s="7" t="inlineStr">
         <is>
-          <t>编辑共享通行证（无ES流量）</t>
+          <t>场景1: walmart / 编辑SharePass状态</t>
         </is>
       </c>
     </row>
@@ -15810,7 +15937,7 @@
       <c r="F410" s="3" t="n"/>
       <c r="G410" s="7" t="inlineStr">
         <is>
-          <t>获取可共享账户列表 — 25%</t>
+          <t>场景1: 默认调用(无入参) / 查询账号列表</t>
         </is>
       </c>
     </row>
@@ -15839,7 +15966,7 @@
       <c r="F411" s="3" t="n"/>
       <c r="G411" s="7" t="inlineStr">
         <is>
-          <t>通过共享通行证获取规则ID列表</t>
+          <t>场景1: walmart / 查询SharePass关联规则ID</t>
         </is>
       </c>
     </row>
@@ -15868,7 +15995,7 @@
       <c r="F412" s="3" t="n"/>
       <c r="G412" s="7" t="inlineStr">
         <is>
-          <t>获取可共享平台列表 — 8%</t>
+          <t>场景1: 默认查询 / 查询可分享平台列表</t>
         </is>
       </c>
     </row>
@@ -15897,7 +16024,7 @@
       <c r="F413" s="3" t="n"/>
       <c r="G413" s="7" t="inlineStr">
         <is>
-          <t>amazon平台分页查询共享通行证列表 — 24%</t>
+          <t>场景1: 默认查询 / 查询SharePass列表</t>
         </is>
       </c>
     </row>
@@ -15926,11 +16053,11 @@
       <c r="F414" s="3" t="n"/>
       <c r="G414" s="7" t="inlineStr">
         <is>
-          <t>创建模板并批量创建(可重复)</t>
-        </is>
-      </c>
-    </row>
-    <row r="415" ht="16" customHeight="1">
+          <t>场景1: walmart / 创建模板[FAIL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="415" ht="32" customHeight="1">
       <c r="A415" s="3" t="n"/>
       <c r="B415" s="3" t="inlineStr">
         <is>
@@ -15955,7 +16082,8 @@
       <c r="F415" s="3" t="n"/>
       <c r="G415" s="7" t="inlineStr">
         <is>
-          <t>删除模板（需有效templateId）</t>
+          <t>场景1: walmart / 清理-删除模板[FAIL]
+场景2: walmart / 清理-删除bulk创建的模板[FAIL]</t>
         </is>
       </c>
     </row>
@@ -15984,11 +16112,11 @@
       <c r="F416" s="3" t="n"/>
       <c r="G416" s="7" t="inlineStr">
         <is>
-          <t>模板收藏切换</t>
-        </is>
-      </c>
-    </row>
-    <row r="417">
+          <t>场景1: walmart / 收藏模板[FAIL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="417" ht="16" customHeight="1">
       <c r="A417" s="3" t="n"/>
       <c r="B417" s="3" t="inlineStr">
         <is>
@@ -16011,7 +16139,11 @@
         </is>
       </c>
       <c r="F417" s="3" t="n"/>
-      <c r="G417" s="3" t="n"/>
+      <c r="G417" s="7" t="inlineStr">
+        <is>
+          <t>场景1: walmart / 批量创建模板</t>
+        </is>
+      </c>
     </row>
     <row r="418" ht="16" customHeight="1">
       <c r="A418" s="3" t="n"/>
@@ -16038,11 +16170,11 @@
       <c r="F418" s="3" t="n"/>
       <c r="G418" s="7" t="inlineStr">
         <is>
-          <t>创建编辑删除分类(可重复)</t>
-        </is>
-      </c>
-    </row>
-    <row r="419">
+          <t>场景1: walmart / 创建分类</t>
+        </is>
+      </c>
+    </row>
+    <row r="419" ht="16" customHeight="1">
       <c r="A419" s="3" t="n"/>
       <c r="B419" s="3" t="inlineStr">
         <is>
@@ -16065,7 +16197,11 @@
         </is>
       </c>
       <c r="F419" s="3" t="n"/>
-      <c r="G419" s="3" t="n"/>
+      <c r="G419" s="7" t="inlineStr">
+        <is>
+          <t>场景1: walmart / 清理-删除分类</t>
+        </is>
+      </c>
     </row>
     <row r="420" ht="16" customHeight="1">
       <c r="A420" s="3" t="n"/>
@@ -16121,7 +16257,7 @@
       <c r="F421" s="3" t="n"/>
       <c r="G421" s="3" t="n"/>
     </row>
-    <row r="422">
+    <row r="422" ht="16" customHeight="1">
       <c r="A422" s="3" t="n"/>
       <c r="B422" s="3" t="inlineStr">
         <is>
@@ -16144,7 +16280,11 @@
         </is>
       </c>
       <c r="F422" s="3" t="n"/>
-      <c r="G422" s="3" t="n"/>
+      <c r="G422" s="7" t="inlineStr">
+        <is>
+          <t>场景1: walmart / 编辑分类</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="3" t="n"/>
@@ -16225,7 +16365,7 @@
       <c r="F425" s="3" t="n"/>
       <c r="G425" s="7" t="inlineStr">
         <is>
-          <t>创建模板并验证editTemplate端点可达(可重复)</t>
+          <t>场景1: walmart / 编辑模板[FAIL]</t>
         </is>
       </c>
     </row>
@@ -16254,8 +16394,8 @@
       <c r="F426" s="3" t="n"/>
       <c r="G426" s="7" t="inlineStr">
         <is>
-          <t>无ruleType过滤查询全部分类 — 40%
-Targeting类型模板分类 — 40%</t>
+          <t>场景1: 默认查询 / 查询分类列表
+场景2: walmart / 查询新建分类的ID</t>
         </is>
       </c>
     </row>
@@ -16284,7 +16424,7 @@
       <c r="F427" s="3" t="n"/>
       <c r="G427" s="7" t="inlineStr">
         <is>
-          <t>获取默认模板分类 — 0.11%</t>
+          <t>场景1: 默认查询 / 查询默认分类列表</t>
         </is>
       </c>
     </row>
@@ -16313,7 +16453,7 @@
       <c r="F428" s="3" t="n"/>
       <c r="G428" s="7" t="inlineStr">
         <is>
-          <t>获取默认模板列表 — 0.15%</t>
+          <t>场景1: 默认查询 / 查询默认模板列表</t>
         </is>
       </c>
     </row>
@@ -16342,11 +16482,11 @@
       <c r="F429" s="3" t="n"/>
       <c r="G429" s="7" t="inlineStr">
         <is>
-          <t>获取模板创建者列表 — 3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="430">
+          <t>场景1: 默认调用(无入参) / 查询模板所有者列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="430" ht="16" customHeight="1">
       <c r="A430" s="3" t="n"/>
       <c r="B430" s="3" t="inlineStr">
         <is>
@@ -16369,9 +16509,13 @@
         </is>
       </c>
       <c r="F430" s="3" t="n"/>
-      <c r="G430" s="3" t="n"/>
-    </row>
-    <row r="431" ht="16" customHeight="1">
+      <c r="G430" s="7" t="inlineStr">
+        <is>
+          <t>场景1: 默认查询 / 查询推荐模板[FAIL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="431" ht="48" customHeight="1">
       <c r="A431" s="3" t="n"/>
       <c r="B431" s="3" t="inlineStr">
         <is>
@@ -16396,7 +16540,9 @@
       <c r="F431" s="3" t="n"/>
       <c r="G431" s="7" t="inlineStr">
         <is>
-          <t>onlyFavorite:true查询收藏模板 — 47%</t>
+          <t>场景1: 按ruleType筛选 / 按ruleType查询模板列表
+场景2: walmart / 查询新建模板的ID[FAIL]
+场景3: walmart / 查询bulk新建模板的ID[FAIL]</t>
         </is>
       </c>
     </row>
@@ -16425,7 +16571,7 @@
       <c r="F432" s="3" t="n"/>
       <c r="G432" s="7" t="inlineStr">
         <is>
-          <t>通过直链分享获取模板列表</t>
+          <t>场景1: 测试账号真实模板 / 查询DirectShare模板列表</t>
         </is>
       </c>
     </row>
@@ -16512,7 +16658,7 @@
       <c r="F435" s="3" t="n"/>
       <c r="G435" s="7" t="inlineStr">
         <is>
-          <t>移动模板到分类(创建临时分类,可重复)</t>
+          <t>场景1: walmart / 移动模板到另一分类[FAIL]</t>
         </is>
       </c>
     </row>
@@ -16570,7 +16716,7 @@
       <c r="F437" s="3" t="n"/>
       <c r="G437" s="7" t="inlineStr">
         <is>
-          <t>按campaignId统计规则数量(无ES流量,TikTok返回405)（无ES流量）</t>
+          <t>场景1: 测试账号真实campaign / 按CampaignId查询规则数量</t>
         </is>
       </c>
     </row>
@@ -16599,7 +16745,7 @@
       <c r="F438" s="3" t="n"/>
       <c r="G438" s="7" t="inlineStr">
         <is>
-          <t>按userId统计TikTok规则数量 — 100%</t>
+          <t>场景1: 测试账号真实user / 按UserId查询规则数量</t>
         </is>
       </c>
     </row>
@@ -16628,7 +16774,7 @@
       <c r="F439" s="3" t="n"/>
       <c r="G439" s="7" t="inlineStr">
         <is>
-          <t>按ruleIds批量获取规则定义(创建临时规则,可重复) — 100%</t>
+          <t>场景1: 测试账号真实规则 / 查询规则定义</t>
         </is>
       </c>
     </row>
@@ -16657,7 +16803,7 @@
       <c r="F440" s="3" t="n"/>
       <c r="G440" s="7" t="inlineStr">
         <is>
-          <t>获取规则类型列表 — 100%</t>
+          <t>场景1: 默认调用(无入参) / 查询规则类型列表</t>
         </is>
       </c>
     </row>

--- a/single-api/services/rule-api/swagger_modules.xlsx
+++ b/single-api/services/rule-api/swagger_modules.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="模块汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="RuleApi" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块汇总" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RuleApi" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -92,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -481,11 +484,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H169"/>
+  <dimension ref="A1:I169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -502,35 +505,40 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>服务(Swagger Title)</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>平台(Platform)</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>模块(Tag)</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>接口数</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>负责人</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Case数</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>通过率</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>接口覆盖率</t>
         </is>
@@ -542,29 +550,34 @@
           <t>us</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>amazon</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>auto-task-controller</t>
         </is>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="E2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>100% (1/1)</t>
         </is>
@@ -572,29 +585,34 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>amazon</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>config-controller</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="E3" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>100% (10/10)</t>
         </is>
@@ -602,29 +620,34 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>amazon</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>data-impact-controller</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="E4" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>100% (5/5)</t>
         </is>
@@ -632,29 +655,34 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>amazon</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>55% (28/51)</t>
         </is>
@@ -662,29 +690,34 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n"/>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>amazon</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>feature-usage-controller</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="E6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>100% (2/2)</t>
         </is>
@@ -692,29 +725,34 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>amazon</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>health-controller</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="E7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>100% (1/1)</t>
         </is>
@@ -722,29 +760,34 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>amazon</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>history-controller</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="E8" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>100% (26/26)</t>
         </is>
@@ -752,49 +795,59 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>amazon</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>migration-controller</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="E9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n"/>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>amazon</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>report-controller</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="E10" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>85% (11/13)</t>
         </is>
@@ -802,29 +855,34 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>amazon</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>share-pass-controller</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="E11" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>100% (9/9)</t>
         </is>
@@ -832,29 +890,34 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n"/>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>amazon</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>template-controller</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="E12" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>73% (16/22)</t>
         </is>
@@ -862,29 +925,34 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>amazon</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>to-event</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="E13" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>80% (4/5)</t>
         </is>
@@ -892,29 +960,34 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>tiktok</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>auto-task-controller</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="E14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>100% (1/1)</t>
         </is>
@@ -922,29 +995,34 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n"/>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>tiktok</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>config-controller</t>
         </is>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="E15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>100% (10/10)</t>
         </is>
@@ -952,29 +1030,34 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n"/>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>tiktok</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>data-impact-controller</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="E16" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>100% (5/5)</t>
         </is>
@@ -982,29 +1065,34 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>tiktok</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>29% (15/51)</t>
         </is>
@@ -1012,29 +1100,34 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n"/>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>tiktok</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>feature-usage-controller</t>
         </is>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="E18" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>100% (2/2)</t>
         </is>
@@ -1042,29 +1135,34 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>tiktok</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>health-controller</t>
         </is>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="E19" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>100% (1/1)</t>
         </is>
@@ -1072,29 +1170,34 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n"/>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>tiktok</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>history-controller</t>
         </is>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="E20" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="4" t="n">
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>96% (25/26)</t>
         </is>
@@ -1102,49 +1205,59 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n"/>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>tiktok</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>migration-controller</t>
         </is>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="E21" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="4" t="n"/>
+      <c r="F21" s="3" t="n"/>
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n"/>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>tiktok</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>report-controller</t>
         </is>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="E22" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="4" t="n">
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>100% (13/13)</t>
         </is>
@@ -1152,29 +1265,34 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>tiktok</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>share-pass-controller</t>
         </is>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="E23" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>100% (9/9)</t>
         </is>
@@ -1182,29 +1300,34 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>tiktok</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>template-controller</t>
         </is>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="E24" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>73% (16/22)</t>
         </is>
@@ -1212,29 +1335,34 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n"/>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>tiktok</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>to-event</t>
         </is>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="E25" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="4" t="n">
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>100% (5/5)</t>
         </is>
@@ -1242,29 +1370,34 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n"/>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>walmart</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>auto-task-controller</t>
         </is>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="E26" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="4" t="n">
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>100% (1/1)</t>
         </is>
@@ -1272,29 +1405,34 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n"/>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>walmart</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>config-controller</t>
         </is>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="E27" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="4" t="n">
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>100% (10/10)</t>
         </is>
@@ -1302,29 +1440,34 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n"/>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>walmart</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>data-impact-controller</t>
         </is>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="E28" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="4" t="n">
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>100% (5/5)</t>
         </is>
@@ -1332,49 +1475,59 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n"/>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>walmart</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="E29" s="3" t="n"/>
       <c r="F29" s="3" t="n"/>
       <c r="G29" s="3" t="n"/>
       <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n"/>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>walmart</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>feature-usage-controller</t>
         </is>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="E30" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="4" t="n">
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>100% (2/2)</t>
         </is>
@@ -1382,29 +1535,34 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n"/>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>walmart</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>health-controller</t>
         </is>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="E31" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="4" t="n">
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>100% (1/1)</t>
         </is>
@@ -1412,29 +1570,34 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n"/>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>walmart</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>history-controller</t>
         </is>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="E32" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" s="4" t="n">
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>100% (26/26)</t>
         </is>
@@ -1442,49 +1605,59 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n"/>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>walmart</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>migration-controller</t>
         </is>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="E33" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E33" s="3" t="n"/>
       <c r="F33" s="3" t="n"/>
       <c r="G33" s="3" t="n"/>
       <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n"/>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>walmart</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>report-controller</t>
         </is>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="E34" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="4" t="n">
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="I34" s="4" t="inlineStr">
         <is>
           <t>85% (11/13)</t>
         </is>
@@ -1492,29 +1665,34 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n"/>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>walmart</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>share-pass-controller</t>
         </is>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="E35" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E35" s="3" t="n"/>
-      <c r="F35" s="4" t="n">
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>100% (9/9)</t>
         </is>
@@ -1522,29 +1700,34 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n"/>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>walmart</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>template-controller</t>
         </is>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="E36" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="4" t="n">
+      <c r="F36" s="3" t="n"/>
+      <c r="G36" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="I36" s="4" t="inlineStr">
         <is>
           <t>73% (16/22)</t>
         </is>
@@ -1552,29 +1735,34 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n"/>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>walmart</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>to-event</t>
         </is>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="E37" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="4" t="n">
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="I37" s="4" t="inlineStr">
         <is>
           <t>80% (4/5)</t>
         </is>
@@ -1582,29 +1770,34 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n"/>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>instacart</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>auto-task-controller</t>
         </is>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="E38" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E38" s="3" t="n"/>
-      <c r="F38" s="4" t="n">
+      <c r="F38" s="3" t="n"/>
+      <c r="G38" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
+      <c r="I38" s="4" t="inlineStr">
         <is>
           <t>100% (1/1)</t>
         </is>
@@ -1612,29 +1805,34 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n"/>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>instacart</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>config-controller</t>
         </is>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="E39" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E39" s="3" t="n"/>
-      <c r="F39" s="4" t="n">
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="I39" s="4" t="inlineStr">
         <is>
           <t>90% (9/10)</t>
         </is>
@@ -1642,29 +1840,34 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n"/>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>instacart</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>data-impact-controller</t>
         </is>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="E40" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E40" s="3" t="n"/>
-      <c r="F40" s="4" t="n">
+      <c r="F40" s="3" t="n"/>
+      <c r="G40" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="I40" s="4" t="inlineStr">
         <is>
           <t>100% (5/5)</t>
         </is>
@@ -1672,29 +1875,34 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n"/>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>instacart</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="4" t="n">
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="H41" s="4" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="I41" s="4" t="inlineStr">
         <is>
           <t>100% (51/51)</t>
         </is>
@@ -1702,29 +1910,34 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n"/>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>instacart</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>feature-usage-controller</t>
         </is>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="E42" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E42" s="3" t="n"/>
-      <c r="F42" s="4" t="n">
+      <c r="F42" s="3" t="n"/>
+      <c r="G42" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="I42" s="4" t="inlineStr">
         <is>
           <t>100% (2/2)</t>
         </is>
@@ -1732,29 +1945,34 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n"/>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>instacart</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>health-controller</t>
         </is>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="E43" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E43" s="3" t="n"/>
-      <c r="F43" s="4" t="n">
+      <c r="F43" s="3" t="n"/>
+      <c r="G43" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="H43" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr">
+      <c r="I43" s="4" t="inlineStr">
         <is>
           <t>100% (1/1)</t>
         </is>
@@ -1762,29 +1980,34 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="n"/>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>instacart</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>history-controller</t>
         </is>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="E44" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="E44" s="3" t="n"/>
-      <c r="F44" s="4" t="n">
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>81%</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
+      <c r="I44" s="4" t="inlineStr">
         <is>
           <t>100% (26/26)</t>
         </is>
@@ -1792,49 +2015,59 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n"/>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>instacart</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>migration-controller</t>
         </is>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="E45" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E45" s="3" t="n"/>
-      <c r="F45" s="4" t="n"/>
+      <c r="F45" s="3" t="n"/>
       <c r="G45" s="4" t="n"/>
       <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n"/>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>instacart</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>report-controller</t>
         </is>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="E46" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E46" s="3" t="n"/>
-      <c r="F46" s="4" t="n">
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="H46" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
+      <c r="I46" s="4" t="inlineStr">
         <is>
           <t>100% (13/13)</t>
         </is>
@@ -1842,29 +2075,34 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n"/>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>instacart</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>share-pass-controller</t>
         </is>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="E47" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E47" s="3" t="n"/>
-      <c r="F47" s="4" t="n">
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="H47" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr">
+      <c r="I47" s="4" t="inlineStr">
         <is>
           <t>100% (9/9)</t>
         </is>
@@ -1872,29 +2110,34 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="n"/>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>instacart</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>template-controller</t>
         </is>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="E48" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="E48" s="3" t="n"/>
-      <c r="F48" s="4" t="n">
+      <c r="F48" s="3" t="n"/>
+      <c r="G48" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="G48" s="4" t="inlineStr">
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
+      <c r="I48" s="4" t="inlineStr">
         <is>
           <t>86% (19/22)</t>
         </is>
@@ -1902,29 +2145,34 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n"/>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>instacart</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>to-event</t>
         </is>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="E49" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E49" s="3" t="n"/>
-      <c r="F49" s="4" t="n">
+      <c r="F49" s="3" t="n"/>
+      <c r="G49" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G49" s="4" t="inlineStr">
+      <c r="H49" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H49" s="4" t="inlineStr">
+      <c r="I49" s="4" t="inlineStr">
         <is>
           <t>100% (5/5)</t>
         </is>
@@ -1932,25 +2180,30 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="n"/>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>criteo</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>auto-task-controller</t>
         </is>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="E50" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E50" s="3" t="n"/>
-      <c r="F50" s="3" t="n">
+      <c r="F50" s="3" t="n"/>
+      <c r="G50" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G50" s="3" t="n"/>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="H50" s="3" t="n"/>
+      <c r="I50" s="3" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -1958,29 +2211,34 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="n"/>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>criteo</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>config-controller</t>
         </is>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="E51" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E51" s="3" t="n"/>
-      <c r="F51" s="4" t="n">
+      <c r="F51" s="3" t="n"/>
+      <c r="G51" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G51" s="4" t="inlineStr">
+      <c r="H51" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr">
+      <c r="I51" s="4" t="inlineStr">
         <is>
           <t>70% (7/10)</t>
         </is>
@@ -1988,25 +2246,30 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="n"/>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>criteo</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>data-impact-controller</t>
         </is>
       </c>
-      <c r="D52" s="4" t="n">
+      <c r="E52" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E52" s="3" t="n"/>
-      <c r="F52" s="3" t="n">
+      <c r="F52" s="3" t="n"/>
+      <c r="G52" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G52" s="3" t="n"/>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="H52" s="3" t="n"/>
+      <c r="I52" s="3" t="inlineStr">
         <is>
           <t>0% (0/5)</t>
         </is>
@@ -2014,29 +2277,34 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="n"/>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>criteo</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="n">
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="E53" s="3" t="n"/>
-      <c r="F53" s="4" t="n">
+      <c r="F53" s="3" t="n"/>
+      <c r="G53" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="G53" s="4" t="inlineStr">
+      <c r="H53" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H53" s="4" t="inlineStr">
+      <c r="I53" s="4" t="inlineStr">
         <is>
           <t>20% (10/51)</t>
         </is>
@@ -2044,25 +2312,30 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="n"/>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>criteo</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>feature-usage-controller</t>
         </is>
       </c>
-      <c r="D54" s="4" t="n">
+      <c r="E54" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E54" s="3" t="n"/>
-      <c r="F54" s="3" t="n">
+      <c r="F54" s="3" t="n"/>
+      <c r="G54" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G54" s="3" t="n"/>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="H54" s="3" t="n"/>
+      <c r="I54" s="3" t="inlineStr">
         <is>
           <t>0% (0/2)</t>
         </is>
@@ -2070,25 +2343,30 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="n"/>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>criteo</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>health-controller</t>
         </is>
       </c>
-      <c r="D55" s="4" t="n">
+      <c r="E55" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E55" s="3" t="n"/>
-      <c r="F55" s="3" t="n">
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G55" s="3" t="n"/>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="H55" s="3" t="n"/>
+      <c r="I55" s="3" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -2096,29 +2374,34 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="n"/>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>criteo</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>history-controller</t>
         </is>
       </c>
-      <c r="D56" s="4" t="n">
+      <c r="E56" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="E56" s="3" t="n"/>
-      <c r="F56" s="4" t="n">
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G56" s="4" t="inlineStr">
+      <c r="H56" s="4" t="inlineStr">
         <is>
           <t>N/A(1 skip)</t>
         </is>
       </c>
-      <c r="H56" s="4" t="inlineStr">
+      <c r="I56" s="4" t="inlineStr">
         <is>
           <t>4% (1/26)</t>
         </is>
@@ -2126,49 +2409,59 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="n"/>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>criteo</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>migration-controller</t>
         </is>
       </c>
-      <c r="D57" s="4" t="n">
+      <c r="E57" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E57" s="3" t="n"/>
       <c r="F57" s="3" t="n"/>
       <c r="G57" s="3" t="n"/>
       <c r="H57" s="3" t="n"/>
+      <c r="I57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n"/>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>criteo</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>report-controller</t>
         </is>
       </c>
-      <c r="D58" s="4" t="n">
+      <c r="E58" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E58" s="3" t="n"/>
-      <c r="F58" s="4" t="n">
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G58" s="4" t="inlineStr">
+      <c r="H58" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr">
+      <c r="I58" s="4" t="inlineStr">
         <is>
           <t>23% (3/13)</t>
         </is>
@@ -2176,29 +2469,34 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="n"/>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>criteo</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>share-pass-controller</t>
         </is>
       </c>
-      <c r="D59" s="4" t="n">
+      <c r="E59" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E59" s="3" t="n"/>
-      <c r="F59" s="4" t="n">
+      <c r="F59" s="3" t="n"/>
+      <c r="G59" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="H59" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H59" s="4" t="inlineStr">
+      <c r="I59" s="4" t="inlineStr">
         <is>
           <t>22% (2/9)</t>
         </is>
@@ -2206,29 +2504,34 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="n"/>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>criteo</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>template-controller</t>
         </is>
       </c>
-      <c r="D60" s="4" t="n">
+      <c r="E60" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="E60" s="3" t="n"/>
-      <c r="F60" s="4" t="n">
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="H60" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
+      <c r="I60" s="4" t="inlineStr">
         <is>
           <t>5% (1/22)</t>
         </is>
@@ -2236,29 +2539,34 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="n"/>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>criteo</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>to-event</t>
         </is>
       </c>
-      <c r="D61" s="4" t="n">
+      <c r="E61" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E61" s="3" t="n"/>
-      <c r="F61" s="4" t="n">
+      <c r="F61" s="3" t="n"/>
+      <c r="G61" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="H61" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H61" s="4" t="inlineStr">
+      <c r="I61" s="4" t="inlineStr">
         <is>
           <t>20% (1/5)</t>
         </is>
@@ -2266,25 +2574,30 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="n"/>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>auto-task-controller</t>
         </is>
       </c>
-      <c r="D62" s="4" t="n">
+      <c r="E62" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E62" s="3" t="n"/>
-      <c r="F62" s="3" t="n">
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G62" s="3" t="n"/>
-      <c r="H62" s="3" t="inlineStr">
+      <c r="H62" s="3" t="n"/>
+      <c r="I62" s="3" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -2292,29 +2605,34 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="n"/>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>config-controller</t>
         </is>
       </c>
-      <c r="D63" s="4" t="n">
+      <c r="E63" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E63" s="3" t="n"/>
-      <c r="F63" s="4" t="n">
+      <c r="F63" s="3" t="n"/>
+      <c r="G63" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="G63" s="4" t="inlineStr">
+      <c r="H63" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H63" s="4" t="inlineStr">
+      <c r="I63" s="4" t="inlineStr">
         <is>
           <t>80% (8/10)</t>
         </is>
@@ -2322,29 +2640,34 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="n"/>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>data-impact-controller</t>
         </is>
       </c>
-      <c r="D64" s="4" t="n">
+      <c r="E64" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E64" s="3" t="n"/>
-      <c r="F64" s="4" t="n">
+      <c r="F64" s="3" t="n"/>
+      <c r="G64" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G64" s="4" t="inlineStr">
+      <c r="H64" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="H64" s="4" t="inlineStr">
+      <c r="I64" s="4" t="inlineStr">
         <is>
           <t>40% (2/5)</t>
         </is>
@@ -2352,29 +2675,34 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="n"/>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="n">
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="E65" s="3" t="n"/>
-      <c r="F65" s="4" t="n">
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="G65" s="4" t="inlineStr">
+      <c r="H65" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H65" s="4" t="inlineStr">
+      <c r="I65" s="4" t="inlineStr">
         <is>
           <t>37% (19/51)</t>
         </is>
@@ -2382,25 +2710,30 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="n"/>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>feature-usage-controller</t>
         </is>
       </c>
-      <c r="D66" s="4" t="n">
+      <c r="E66" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E66" s="3" t="n"/>
-      <c r="F66" s="3" t="n">
+      <c r="F66" s="3" t="n"/>
+      <c r="G66" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G66" s="3" t="n"/>
-      <c r="H66" s="3" t="inlineStr">
+      <c r="H66" s="3" t="n"/>
+      <c r="I66" s="3" t="inlineStr">
         <is>
           <t>0% (0/2)</t>
         </is>
@@ -2408,25 +2741,30 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="n"/>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>health-controller</t>
         </is>
       </c>
-      <c r="D67" s="4" t="n">
+      <c r="E67" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E67" s="3" t="n"/>
-      <c r="F67" s="3" t="n">
+      <c r="F67" s="3" t="n"/>
+      <c r="G67" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G67" s="3" t="n"/>
-      <c r="H67" s="3" t="inlineStr">
+      <c r="H67" s="3" t="n"/>
+      <c r="I67" s="3" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -2434,29 +2772,34 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="n"/>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>history-controller</t>
         </is>
       </c>
-      <c r="D68" s="4" t="n">
+      <c r="E68" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="E68" s="3" t="n"/>
-      <c r="F68" s="4" t="n">
+      <c r="F68" s="3" t="n"/>
+      <c r="G68" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="G68" s="4" t="inlineStr">
+      <c r="H68" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H68" s="4" t="inlineStr">
+      <c r="I68" s="4" t="inlineStr">
         <is>
           <t>35% (9/26)</t>
         </is>
@@ -2464,49 +2807,59 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="n"/>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>migration-controller</t>
         </is>
       </c>
-      <c r="D69" s="4" t="n">
+      <c r="E69" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E69" s="3" t="n"/>
       <c r="F69" s="3" t="n"/>
       <c r="G69" s="3" t="n"/>
       <c r="H69" s="3" t="n"/>
+      <c r="I69" s="3" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n"/>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>report-controller</t>
         </is>
       </c>
-      <c r="D70" s="4" t="n">
+      <c r="E70" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E70" s="3" t="n"/>
-      <c r="F70" s="4" t="n">
+      <c r="F70" s="3" t="n"/>
+      <c r="G70" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="G70" s="4" t="inlineStr">
+      <c r="H70" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H70" s="4" t="inlineStr">
+      <c r="I70" s="4" t="inlineStr">
         <is>
           <t>100% (13/13)</t>
         </is>
@@ -2514,29 +2867,34 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="n"/>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>share-pass-controller</t>
         </is>
       </c>
-      <c r="D71" s="4" t="n">
+      <c r="E71" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E71" s="3" t="n"/>
-      <c r="F71" s="4" t="n">
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G71" s="4" t="inlineStr">
+      <c r="H71" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H71" s="4" t="inlineStr">
+      <c r="I71" s="4" t="inlineStr">
         <is>
           <t>22% (2/9)</t>
         </is>
@@ -2544,29 +2902,34 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="n"/>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>template-controller</t>
         </is>
       </c>
-      <c r="D72" s="4" t="n">
+      <c r="E72" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="E72" s="3" t="n"/>
-      <c r="F72" s="4" t="n">
+      <c r="F72" s="3" t="n"/>
+      <c r="G72" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G72" s="4" t="inlineStr">
+      <c r="H72" s="4" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
       </c>
-      <c r="H72" s="4" t="inlineStr">
+      <c r="I72" s="4" t="inlineStr">
         <is>
           <t>77% (17/22)</t>
         </is>
@@ -2574,29 +2937,34 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="n"/>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>to-event</t>
         </is>
       </c>
-      <c r="D73" s="4" t="n">
+      <c r="E73" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E73" s="3" t="n"/>
-      <c r="F73" s="4" t="n">
+      <c r="F73" s="3" t="n"/>
+      <c r="G73" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G73" s="4" t="inlineStr">
+      <c r="H73" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H73" s="4" t="inlineStr">
+      <c r="I73" s="4" t="inlineStr">
         <is>
           <t>60% (3/5)</t>
         </is>
@@ -2604,29 +2972,34 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="n"/>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>kroger</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>auto-task-controller</t>
         </is>
       </c>
-      <c r="D74" s="4" t="n">
+      <c r="E74" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E74" s="3" t="n"/>
-      <c r="F74" s="4" t="n">
+      <c r="F74" s="3" t="n"/>
+      <c r="G74" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G74" s="4" t="inlineStr">
+      <c r="H74" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr">
+      <c r="I74" s="4" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -2634,29 +3007,34 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="n"/>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>kroger</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>config-controller</t>
         </is>
       </c>
-      <c r="D75" s="4" t="n">
+      <c r="E75" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E75" s="3" t="n"/>
-      <c r="F75" s="4" t="n">
+      <c r="F75" s="3" t="n"/>
+      <c r="G75" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G75" s="4" t="inlineStr">
+      <c r="H75" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H75" s="4" t="inlineStr">
+      <c r="I75" s="4" t="inlineStr">
         <is>
           <t>70% (7/10)</t>
         </is>
@@ -2664,29 +3042,34 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="n"/>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>kroger</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>data-impact-controller</t>
         </is>
       </c>
-      <c r="D76" s="4" t="n">
+      <c r="E76" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E76" s="3" t="n"/>
-      <c r="F76" s="4" t="n">
+      <c r="F76" s="3" t="n"/>
+      <c r="G76" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G76" s="4" t="inlineStr">
+      <c r="H76" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H76" s="4" t="inlineStr">
+      <c r="I76" s="4" t="inlineStr">
         <is>
           <t>0% (0/5)</t>
         </is>
@@ -2694,29 +3077,34 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="n"/>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>kroger</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="n">
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="E77" s="3" t="n"/>
-      <c r="F77" s="4" t="n">
+      <c r="F77" s="3" t="n"/>
+      <c r="G77" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="G77" s="4" t="inlineStr">
+      <c r="H77" s="4" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="H77" s="4" t="inlineStr">
+      <c r="I77" s="4" t="inlineStr">
         <is>
           <t>73% (37/51)</t>
         </is>
@@ -2724,29 +3112,34 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="n"/>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>kroger</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>feature-usage-controller</t>
         </is>
       </c>
-      <c r="D78" s="4" t="n">
+      <c r="E78" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E78" s="3" t="n"/>
-      <c r="F78" s="4" t="n">
+      <c r="F78" s="3" t="n"/>
+      <c r="G78" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G78" s="4" t="inlineStr">
+      <c r="H78" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H78" s="4" t="inlineStr">
+      <c r="I78" s="4" t="inlineStr">
         <is>
           <t>0% (0/2)</t>
         </is>
@@ -2754,29 +3147,34 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="n"/>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>kroger</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>health-controller</t>
         </is>
       </c>
-      <c r="D79" s="4" t="n">
+      <c r="E79" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E79" s="3" t="n"/>
-      <c r="F79" s="4" t="n">
+      <c r="F79" s="3" t="n"/>
+      <c r="G79" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G79" s="4" t="inlineStr">
+      <c r="H79" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H79" s="4" t="inlineStr">
+      <c r="I79" s="4" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -2784,29 +3182,34 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="n"/>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>kroger</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>history-controller</t>
         </is>
       </c>
-      <c r="D80" s="4" t="n">
+      <c r="E80" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="E80" s="3" t="n"/>
-      <c r="F80" s="4" t="n">
+      <c r="F80" s="3" t="n"/>
+      <c r="G80" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="G80" s="4" t="inlineStr">
+      <c r="H80" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H80" s="4" t="inlineStr">
+      <c r="I80" s="4" t="inlineStr">
         <is>
           <t>31% (8/26)</t>
         </is>
@@ -2814,49 +3217,59 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="n"/>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>kroger</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>migration-controller</t>
         </is>
       </c>
-      <c r="D81" s="4" t="n">
+      <c r="E81" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E81" s="3" t="n"/>
       <c r="F81" s="3" t="n"/>
       <c r="G81" s="3" t="n"/>
       <c r="H81" s="3" t="n"/>
+      <c r="I81" s="3" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n"/>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>kroger</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>report-controller</t>
         </is>
       </c>
-      <c r="D82" s="4" t="n">
+      <c r="E82" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E82" s="3" t="n"/>
-      <c r="F82" s="4" t="n">
+      <c r="F82" s="3" t="n"/>
+      <c r="G82" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G82" s="4" t="inlineStr">
+      <c r="H82" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H82" s="4" t="inlineStr">
+      <c r="I82" s="4" t="inlineStr">
         <is>
           <t>8% (1/13)</t>
         </is>
@@ -2864,29 +3277,34 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="n"/>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>kroger</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>share-pass-controller</t>
         </is>
       </c>
-      <c r="D83" s="4" t="n">
+      <c r="E83" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E83" s="3" t="n"/>
-      <c r="F83" s="4" t="n">
+      <c r="F83" s="3" t="n"/>
+      <c r="G83" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G83" s="4" t="inlineStr">
+      <c r="H83" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H83" s="4" t="inlineStr">
+      <c r="I83" s="4" t="inlineStr">
         <is>
           <t>22% (2/9)</t>
         </is>
@@ -2894,29 +3312,34 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="n"/>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>kroger</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>template-controller</t>
         </is>
       </c>
-      <c r="D84" s="4" t="n">
+      <c r="E84" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="E84" s="3" t="n"/>
-      <c r="F84" s="4" t="n">
+      <c r="F84" s="3" t="n"/>
+      <c r="G84" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="G84" s="4" t="inlineStr">
+      <c r="H84" s="4" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
       </c>
-      <c r="H84" s="4" t="inlineStr">
+      <c r="I84" s="4" t="inlineStr">
         <is>
           <t>77% (17/22)</t>
         </is>
@@ -2924,29 +3347,34 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="n"/>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>kroger</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>to-event</t>
         </is>
       </c>
-      <c r="D85" s="4" t="n">
+      <c r="E85" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E85" s="3" t="n"/>
-      <c r="F85" s="4" t="n">
+      <c r="F85" s="3" t="n"/>
+      <c r="G85" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G85" s="4" t="inlineStr">
+      <c r="H85" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H85" s="4" t="inlineStr">
+      <c r="I85" s="4" t="inlineStr">
         <is>
           <t>40% (2/5)</t>
         </is>
@@ -2954,25 +3382,30 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="n"/>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>chewy</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t>auto-task-controller</t>
         </is>
       </c>
-      <c r="D86" s="4" t="n">
+      <c r="E86" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E86" s="3" t="n"/>
-      <c r="F86" s="4" t="n">
+      <c r="F86" s="3" t="n"/>
+      <c r="G86" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G86" s="4" t="n"/>
-      <c r="H86" s="4" t="inlineStr">
+      <c r="H86" s="4" t="n"/>
+      <c r="I86" s="4" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -2980,29 +3413,34 @@
     </row>
     <row r="87">
       <c r="A87" s="3" t="n"/>
-      <c r="B87" s="3" t="inlineStr">
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t>chewy</t>
         </is>
       </c>
-      <c r="C87" s="3" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>config-controller</t>
         </is>
       </c>
-      <c r="D87" s="4" t="n">
+      <c r="E87" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E87" s="3" t="n"/>
-      <c r="F87" s="4" t="n">
+      <c r="F87" s="3" t="n"/>
+      <c r="G87" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G87" s="4" t="inlineStr">
+      <c r="H87" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H87" s="4" t="inlineStr">
+      <c r="I87" s="4" t="inlineStr">
         <is>
           <t>70% (7/10)</t>
         </is>
@@ -3010,25 +3448,30 @@
     </row>
     <row r="88">
       <c r="A88" s="3" t="n"/>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>chewy</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>data-impact-controller</t>
         </is>
       </c>
-      <c r="D88" s="4" t="n">
+      <c r="E88" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E88" s="3" t="n"/>
-      <c r="F88" s="4" t="n">
+      <c r="F88" s="3" t="n"/>
+      <c r="G88" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G88" s="4" t="n"/>
-      <c r="H88" s="4" t="inlineStr">
+      <c r="H88" s="4" t="n"/>
+      <c r="I88" s="4" t="inlineStr">
         <is>
           <t>0% (0/5)</t>
         </is>
@@ -3036,29 +3479,34 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="n"/>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B89" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>chewy</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="n">
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="E89" s="3" t="n"/>
-      <c r="F89" s="4" t="n">
+      <c r="F89" s="3" t="n"/>
+      <c r="G89" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="G89" s="4" t="inlineStr">
+      <c r="H89" s="4" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="H89" s="4" t="inlineStr">
+      <c r="I89" s="4" t="inlineStr">
         <is>
           <t>75% (38/51)</t>
         </is>
@@ -3066,25 +3514,30 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="n"/>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="B90" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>chewy</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>feature-usage-controller</t>
         </is>
       </c>
-      <c r="D90" s="4" t="n">
+      <c r="E90" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E90" s="3" t="n"/>
-      <c r="F90" s="4" t="n">
+      <c r="F90" s="3" t="n"/>
+      <c r="G90" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G90" s="4" t="n"/>
-      <c r="H90" s="4" t="inlineStr">
+      <c r="H90" s="4" t="n"/>
+      <c r="I90" s="4" t="inlineStr">
         <is>
           <t>0% (0/2)</t>
         </is>
@@ -3092,25 +3545,30 @@
     </row>
     <row r="91">
       <c r="A91" s="3" t="n"/>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="B91" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>chewy</t>
         </is>
       </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>health-controller</t>
         </is>
       </c>
-      <c r="D91" s="4" t="n">
+      <c r="E91" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E91" s="3" t="n"/>
-      <c r="F91" s="4" t="n">
+      <c r="F91" s="3" t="n"/>
+      <c r="G91" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G91" s="4" t="n"/>
-      <c r="H91" s="4" t="inlineStr">
+      <c r="H91" s="4" t="n"/>
+      <c r="I91" s="4" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -3118,29 +3576,34 @@
     </row>
     <row r="92">
       <c r="A92" s="3" t="n"/>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
         <is>
           <t>chewy</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>history-controller</t>
         </is>
       </c>
-      <c r="D92" s="4" t="n">
+      <c r="E92" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="E92" s="3" t="n"/>
-      <c r="F92" s="4" t="n">
+      <c r="F92" s="3" t="n"/>
+      <c r="G92" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G92" s="4" t="inlineStr">
+      <c r="H92" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H92" s="4" t="inlineStr">
+      <c r="I92" s="4" t="inlineStr">
         <is>
           <t>38% (10/26)</t>
         </is>
@@ -3148,49 +3611,59 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="n"/>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B93" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
         <is>
           <t>chewy</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>migration-controller</t>
         </is>
       </c>
-      <c r="D93" s="4" t="n">
+      <c r="E93" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E93" s="3" t="n"/>
       <c r="F93" s="3" t="n"/>
       <c r="G93" s="3" t="n"/>
       <c r="H93" s="3" t="n"/>
+      <c r="I93" s="3" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n"/>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t>chewy</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t>report-controller</t>
         </is>
       </c>
-      <c r="D94" s="4" t="n">
+      <c r="E94" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E94" s="3" t="n"/>
-      <c r="F94" s="4" t="n">
+      <c r="F94" s="3" t="n"/>
+      <c r="G94" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G94" s="4" t="inlineStr">
+      <c r="H94" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H94" s="4" t="inlineStr">
+      <c r="I94" s="4" t="inlineStr">
         <is>
           <t>8% (1/13)</t>
         </is>
@@ -3198,29 +3671,34 @@
     </row>
     <row r="95">
       <c r="A95" s="3" t="n"/>
-      <c r="B95" s="3" t="inlineStr">
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t>chewy</t>
         </is>
       </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>share-pass-controller</t>
         </is>
       </c>
-      <c r="D95" s="4" t="n">
+      <c r="E95" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E95" s="3" t="n"/>
-      <c r="F95" s="4" t="n">
+      <c r="F95" s="3" t="n"/>
+      <c r="G95" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G95" s="4" t="inlineStr">
+      <c r="H95" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H95" s="4" t="inlineStr">
+      <c r="I95" s="4" t="inlineStr">
         <is>
           <t>22% (2/9)</t>
         </is>
@@ -3228,29 +3706,34 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="n"/>
-      <c r="B96" s="3" t="inlineStr">
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
         <is>
           <t>chewy</t>
         </is>
       </c>
-      <c r="C96" s="3" t="inlineStr">
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>template-controller</t>
         </is>
       </c>
-      <c r="D96" s="4" t="n">
+      <c r="E96" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="E96" s="3" t="n"/>
-      <c r="F96" s="4" t="n">
+      <c r="F96" s="3" t="n"/>
+      <c r="G96" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="G96" s="4" t="inlineStr">
+      <c r="H96" s="4" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
       </c>
-      <c r="H96" s="4" t="inlineStr">
+      <c r="I96" s="4" t="inlineStr">
         <is>
           <t>77% (17/22)</t>
         </is>
@@ -3258,29 +3741,34 @@
     </row>
     <row r="97">
       <c r="A97" s="3" t="n"/>
-      <c r="B97" s="3" t="inlineStr">
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
         <is>
           <t>chewy</t>
         </is>
       </c>
-      <c r="C97" s="3" t="inlineStr">
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t>to-event</t>
         </is>
       </c>
-      <c r="D97" s="4" t="n">
+      <c r="E97" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E97" s="3" t="n"/>
-      <c r="F97" s="4" t="n">
+      <c r="F97" s="3" t="n"/>
+      <c r="G97" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G97" s="4" t="inlineStr">
+      <c r="H97" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H97" s="4" t="inlineStr">
+      <c r="I97" s="4" t="inlineStr">
         <is>
           <t>40% (2/5)</t>
         </is>
@@ -3288,29 +3776,34 @@
     </row>
     <row r="98">
       <c r="A98" s="3" t="n"/>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
         <is>
           <t>citrus</t>
         </is>
       </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>auto-task-controller</t>
         </is>
       </c>
-      <c r="D98" s="4" t="n">
+      <c r="E98" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E98" s="3" t="n"/>
-      <c r="F98" s="4" t="n">
+      <c r="F98" s="3" t="n"/>
+      <c r="G98" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G98" s="4" t="inlineStr">
+      <c r="H98" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H98" s="4" t="inlineStr">
+      <c r="I98" s="4" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -3318,29 +3811,34 @@
     </row>
     <row r="99">
       <c r="A99" s="3" t="n"/>
-      <c r="B99" s="3" t="inlineStr">
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>citrus</t>
         </is>
       </c>
-      <c r="C99" s="3" t="inlineStr">
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>config-controller</t>
         </is>
       </c>
-      <c r="D99" s="4" t="n">
+      <c r="E99" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E99" s="3" t="n"/>
-      <c r="F99" s="4" t="n">
+      <c r="F99" s="3" t="n"/>
+      <c r="G99" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G99" s="4" t="inlineStr">
+      <c r="H99" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H99" s="4" t="inlineStr">
+      <c r="I99" s="4" t="inlineStr">
         <is>
           <t>70% (7/10)</t>
         </is>
@@ -3348,29 +3846,34 @@
     </row>
     <row r="100">
       <c r="A100" s="3" t="n"/>
-      <c r="B100" s="3" t="inlineStr">
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>citrus</t>
         </is>
       </c>
-      <c r="C100" s="3" t="inlineStr">
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>data-impact-controller</t>
         </is>
       </c>
-      <c r="D100" s="4" t="n">
+      <c r="E100" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E100" s="3" t="n"/>
-      <c r="F100" s="4" t="n">
+      <c r="F100" s="3" t="n"/>
+      <c r="G100" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G100" s="4" t="inlineStr">
+      <c r="H100" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H100" s="4" t="inlineStr">
+      <c r="I100" s="4" t="inlineStr">
         <is>
           <t>40% (2/5)</t>
         </is>
@@ -3378,29 +3881,34 @@
     </row>
     <row r="101">
       <c r="A101" s="3" t="n"/>
-      <c r="B101" s="3" t="inlineStr">
+      <c r="B101" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
         <is>
           <t>citrus</t>
         </is>
       </c>
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="n">
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="E101" s="3" t="n"/>
-      <c r="F101" s="4" t="n">
+      <c r="F101" s="3" t="n"/>
+      <c r="G101" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="G101" s="4" t="inlineStr">
+      <c r="H101" s="4" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
       </c>
-      <c r="H101" s="4" t="inlineStr">
+      <c r="I101" s="4" t="inlineStr">
         <is>
           <t>35% (18/51)</t>
         </is>
@@ -3408,29 +3916,34 @@
     </row>
     <row r="102">
       <c r="A102" s="3" t="n"/>
-      <c r="B102" s="3" t="inlineStr">
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>citrus</t>
         </is>
       </c>
-      <c r="C102" s="3" t="inlineStr">
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>feature-usage-controller</t>
         </is>
       </c>
-      <c r="D102" s="4" t="n">
+      <c r="E102" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E102" s="3" t="n"/>
-      <c r="F102" s="4" t="n">
+      <c r="F102" s="3" t="n"/>
+      <c r="G102" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G102" s="4" t="inlineStr">
+      <c r="H102" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H102" s="4" t="inlineStr">
+      <c r="I102" s="4" t="inlineStr">
         <is>
           <t>0% (0/2)</t>
         </is>
@@ -3438,29 +3951,34 @@
     </row>
     <row r="103">
       <c r="A103" s="3" t="n"/>
-      <c r="B103" s="3" t="inlineStr">
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
         <is>
           <t>citrus</t>
         </is>
       </c>
-      <c r="C103" s="3" t="inlineStr">
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t>health-controller</t>
         </is>
       </c>
-      <c r="D103" s="4" t="n">
+      <c r="E103" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E103" s="3" t="n"/>
-      <c r="F103" s="4" t="n">
+      <c r="F103" s="3" t="n"/>
+      <c r="G103" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G103" s="4" t="inlineStr">
+      <c r="H103" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H103" s="4" t="inlineStr">
+      <c r="I103" s="4" t="inlineStr">
         <is>
           <t>100% (1/1)</t>
         </is>
@@ -3468,29 +3986,34 @@
     </row>
     <row r="104">
       <c r="A104" s="3" t="n"/>
-      <c r="B104" s="3" t="inlineStr">
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
         <is>
           <t>citrus</t>
         </is>
       </c>
-      <c r="C104" s="3" t="inlineStr">
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>history-controller</t>
         </is>
       </c>
-      <c r="D104" s="4" t="n">
+      <c r="E104" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="E104" s="3" t="n"/>
-      <c r="F104" s="4" t="n">
+      <c r="F104" s="3" t="n"/>
+      <c r="G104" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="G104" s="4" t="inlineStr">
+      <c r="H104" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H104" s="4" t="inlineStr">
+      <c r="I104" s="4" t="inlineStr">
         <is>
           <t>62% (16/26)</t>
         </is>
@@ -3498,49 +4021,59 @@
     </row>
     <row r="105">
       <c r="A105" s="3" t="n"/>
-      <c r="B105" s="3" t="inlineStr">
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
         <is>
           <t>citrus</t>
         </is>
       </c>
-      <c r="C105" s="3" t="inlineStr">
+      <c r="D105" s="3" t="inlineStr">
         <is>
           <t>migration-controller</t>
         </is>
       </c>
-      <c r="D105" s="4" t="n">
+      <c r="E105" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E105" s="3" t="n"/>
       <c r="F105" s="3" t="n"/>
       <c r="G105" s="3" t="n"/>
       <c r="H105" s="3" t="n"/>
+      <c r="I105" s="3" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n"/>
-      <c r="B106" s="3" t="inlineStr">
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
         <is>
           <t>citrus</t>
         </is>
       </c>
-      <c r="C106" s="3" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>report-controller</t>
         </is>
       </c>
-      <c r="D106" s="4" t="n">
+      <c r="E106" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E106" s="3" t="n"/>
-      <c r="F106" s="4" t="n">
+      <c r="F106" s="3" t="n"/>
+      <c r="G106" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G106" s="4" t="inlineStr">
+      <c r="H106" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H106" s="4" t="inlineStr">
+      <c r="I106" s="4" t="inlineStr">
         <is>
           <t>23% (3/13)</t>
         </is>
@@ -3548,29 +4081,34 @@
     </row>
     <row r="107">
       <c r="A107" s="3" t="n"/>
-      <c r="B107" s="3" t="inlineStr">
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
         <is>
           <t>citrus</t>
         </is>
       </c>
-      <c r="C107" s="3" t="inlineStr">
+      <c r="D107" s="3" t="inlineStr">
         <is>
           <t>share-pass-controller</t>
         </is>
       </c>
-      <c r="D107" s="4" t="n">
+      <c r="E107" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E107" s="3" t="n"/>
-      <c r="F107" s="4" t="n">
+      <c r="F107" s="3" t="n"/>
+      <c r="G107" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G107" s="4" t="inlineStr">
+      <c r="H107" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H107" s="4" t="inlineStr">
+      <c r="I107" s="4" t="inlineStr">
         <is>
           <t>22% (2/9)</t>
         </is>
@@ -3578,29 +4116,34 @@
     </row>
     <row r="108">
       <c r="A108" s="3" t="n"/>
-      <c r="B108" s="3" t="inlineStr">
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
         <is>
           <t>citrus</t>
         </is>
       </c>
-      <c r="C108" s="3" t="inlineStr">
+      <c r="D108" s="3" t="inlineStr">
         <is>
           <t>template-controller</t>
         </is>
       </c>
-      <c r="D108" s="4" t="n">
+      <c r="E108" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="E108" s="3" t="n"/>
-      <c r="F108" s="4" t="n">
+      <c r="F108" s="3" t="n"/>
+      <c r="G108" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="G108" s="4" t="inlineStr">
+      <c r="H108" s="4" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
       </c>
-      <c r="H108" s="4" t="inlineStr">
+      <c r="I108" s="4" t="inlineStr">
         <is>
           <t>77% (17/22)</t>
         </is>
@@ -3608,29 +4151,34 @@
     </row>
     <row r="109">
       <c r="A109" s="3" t="n"/>
-      <c r="B109" s="3" t="inlineStr">
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
         <is>
           <t>citrus</t>
         </is>
       </c>
-      <c r="C109" s="3" t="inlineStr">
+      <c r="D109" s="3" t="inlineStr">
         <is>
           <t>to-event</t>
         </is>
       </c>
-      <c r="D109" s="4" t="n">
+      <c r="E109" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E109" s="3" t="n"/>
-      <c r="F109" s="4" t="n">
+      <c r="F109" s="3" t="n"/>
+      <c r="G109" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G109" s="4" t="inlineStr">
+      <c r="H109" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H109" s="4" t="inlineStr">
+      <c r="I109" s="4" t="inlineStr">
         <is>
           <t>40% (2/5)</t>
         </is>
@@ -3638,25 +4186,30 @@
     </row>
     <row r="110">
       <c r="A110" s="3" t="n"/>
-      <c r="B110" s="3" t="inlineStr">
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
         <is>
           <t>doordash</t>
         </is>
       </c>
-      <c r="C110" s="3" t="inlineStr">
+      <c r="D110" s="3" t="inlineStr">
         <is>
           <t>auto-task-controller</t>
         </is>
       </c>
-      <c r="D110" s="4" t="n">
+      <c r="E110" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E110" s="3" t="n"/>
-      <c r="F110" s="3" t="n">
+      <c r="F110" s="3" t="n"/>
+      <c r="G110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G110" s="3" t="n"/>
-      <c r="H110" s="3" t="inlineStr">
+      <c r="H110" s="3" t="n"/>
+      <c r="I110" s="3" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -3664,29 +4217,34 @@
     </row>
     <row r="111">
       <c r="A111" s="3" t="n"/>
-      <c r="B111" s="3" t="inlineStr">
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
         <is>
           <t>doordash</t>
         </is>
       </c>
-      <c r="C111" s="3" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t>config-controller</t>
         </is>
       </c>
-      <c r="D111" s="4" t="n">
+      <c r="E111" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E111" s="3" t="n"/>
-      <c r="F111" s="4" t="n">
+      <c r="F111" s="3" t="n"/>
+      <c r="G111" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G111" s="4" t="inlineStr">
+      <c r="H111" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H111" s="4" t="inlineStr">
+      <c r="I111" s="4" t="inlineStr">
         <is>
           <t>80% (8/10)</t>
         </is>
@@ -3694,29 +4252,34 @@
     </row>
     <row r="112">
       <c r="A112" s="3" t="n"/>
-      <c r="B112" s="3" t="inlineStr">
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
         <is>
           <t>doordash</t>
         </is>
       </c>
-      <c r="C112" s="3" t="inlineStr">
+      <c r="D112" s="3" t="inlineStr">
         <is>
           <t>data-impact-controller</t>
         </is>
       </c>
-      <c r="D112" s="4" t="n">
+      <c r="E112" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E112" s="3" t="n"/>
-      <c r="F112" s="4" t="n">
+      <c r="F112" s="3" t="n"/>
+      <c r="G112" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G112" s="4" t="inlineStr">
+      <c r="H112" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="H112" s="4" t="inlineStr">
+      <c r="I112" s="4" t="inlineStr">
         <is>
           <t>40% (2/5)</t>
         </is>
@@ -3724,29 +4287,34 @@
     </row>
     <row r="113">
       <c r="A113" s="3" t="n"/>
-      <c r="B113" s="3" t="inlineStr">
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
         <is>
           <t>doordash</t>
         </is>
       </c>
-      <c r="C113" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D113" s="4" t="n">
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="E113" s="3" t="n"/>
-      <c r="F113" s="4" t="n">
+      <c r="F113" s="3" t="n"/>
+      <c r="G113" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="G113" s="4" t="inlineStr">
+      <c r="H113" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H113" s="4" t="inlineStr">
+      <c r="I113" s="4" t="inlineStr">
         <is>
           <t>31% (16/51)</t>
         </is>
@@ -3754,25 +4322,30 @@
     </row>
     <row r="114">
       <c r="A114" s="3" t="n"/>
-      <c r="B114" s="3" t="inlineStr">
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
         <is>
           <t>doordash</t>
         </is>
       </c>
-      <c r="C114" s="3" t="inlineStr">
+      <c r="D114" s="3" t="inlineStr">
         <is>
           <t>feature-usage-controller</t>
         </is>
       </c>
-      <c r="D114" s="4" t="n">
+      <c r="E114" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E114" s="3" t="n"/>
-      <c r="F114" s="3" t="n">
+      <c r="F114" s="3" t="n"/>
+      <c r="G114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G114" s="3" t="n"/>
-      <c r="H114" s="3" t="inlineStr">
+      <c r="H114" s="3" t="n"/>
+      <c r="I114" s="3" t="inlineStr">
         <is>
           <t>0% (0/2)</t>
         </is>
@@ -3780,25 +4353,30 @@
     </row>
     <row r="115">
       <c r="A115" s="3" t="n"/>
-      <c r="B115" s="3" t="inlineStr">
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
         <is>
           <t>doordash</t>
         </is>
       </c>
-      <c r="C115" s="3" t="inlineStr">
+      <c r="D115" s="3" t="inlineStr">
         <is>
           <t>health-controller</t>
         </is>
       </c>
-      <c r="D115" s="4" t="n">
+      <c r="E115" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E115" s="3" t="n"/>
-      <c r="F115" s="3" t="n">
+      <c r="F115" s="3" t="n"/>
+      <c r="G115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G115" s="3" t="n"/>
-      <c r="H115" s="3" t="inlineStr">
+      <c r="H115" s="3" t="n"/>
+      <c r="I115" s="3" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -3806,29 +4384,34 @@
     </row>
     <row r="116">
       <c r="A116" s="3" t="n"/>
-      <c r="B116" s="3" t="inlineStr">
+      <c r="B116" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
         <is>
           <t>doordash</t>
         </is>
       </c>
-      <c r="C116" s="3" t="inlineStr">
+      <c r="D116" s="3" t="inlineStr">
         <is>
           <t>history-controller</t>
         </is>
       </c>
-      <c r="D116" s="4" t="n">
+      <c r="E116" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="E116" s="3" t="n"/>
-      <c r="F116" s="4" t="n">
+      <c r="F116" s="3" t="n"/>
+      <c r="G116" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="G116" s="4" t="inlineStr">
+      <c r="H116" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H116" s="4" t="inlineStr">
+      <c r="I116" s="4" t="inlineStr">
         <is>
           <t>54% (14/26)</t>
         </is>
@@ -3836,49 +4419,59 @@
     </row>
     <row r="117">
       <c r="A117" s="3" t="n"/>
-      <c r="B117" s="3" t="inlineStr">
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
         <is>
           <t>doordash</t>
         </is>
       </c>
-      <c r="C117" s="3" t="inlineStr">
+      <c r="D117" s="3" t="inlineStr">
         <is>
           <t>migration-controller</t>
         </is>
       </c>
-      <c r="D117" s="4" t="n">
+      <c r="E117" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E117" s="3" t="n"/>
       <c r="F117" s="3" t="n"/>
       <c r="G117" s="3" t="n"/>
       <c r="H117" s="3" t="n"/>
+      <c r="I117" s="3" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n"/>
-      <c r="B118" s="3" t="inlineStr">
+      <c r="B118" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
         <is>
           <t>doordash</t>
         </is>
       </c>
-      <c r="C118" s="3" t="inlineStr">
+      <c r="D118" s="3" t="inlineStr">
         <is>
           <t>report-controller</t>
         </is>
       </c>
-      <c r="D118" s="4" t="n">
+      <c r="E118" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E118" s="3" t="n"/>
-      <c r="F118" s="4" t="n">
+      <c r="F118" s="3" t="n"/>
+      <c r="G118" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G118" s="4" t="inlineStr">
+      <c r="H118" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H118" s="4" t="inlineStr">
+      <c r="I118" s="4" t="inlineStr">
         <is>
           <t>23% (3/13)</t>
         </is>
@@ -3886,29 +4479,34 @@
     </row>
     <row r="119">
       <c r="A119" s="3" t="n"/>
-      <c r="B119" s="3" t="inlineStr">
+      <c r="B119" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
         <is>
           <t>doordash</t>
         </is>
       </c>
-      <c r="C119" s="3" t="inlineStr">
+      <c r="D119" s="3" t="inlineStr">
         <is>
           <t>share-pass-controller</t>
         </is>
       </c>
-      <c r="D119" s="4" t="n">
+      <c r="E119" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E119" s="3" t="n"/>
-      <c r="F119" s="4" t="n">
+      <c r="F119" s="3" t="n"/>
+      <c r="G119" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G119" s="4" t="inlineStr">
+      <c r="H119" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H119" s="4" t="inlineStr">
+      <c r="I119" s="4" t="inlineStr">
         <is>
           <t>22% (2/9)</t>
         </is>
@@ -3916,29 +4514,34 @@
     </row>
     <row r="120">
       <c r="A120" s="3" t="n"/>
-      <c r="B120" s="3" t="inlineStr">
+      <c r="B120" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
         <is>
           <t>doordash</t>
         </is>
       </c>
-      <c r="C120" s="3" t="inlineStr">
+      <c r="D120" s="3" t="inlineStr">
         <is>
           <t>template-controller</t>
         </is>
       </c>
-      <c r="D120" s="4" t="n">
+      <c r="E120" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="E120" s="3" t="n"/>
-      <c r="F120" s="4" t="n">
+      <c r="F120" s="3" t="n"/>
+      <c r="G120" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G120" s="4" t="inlineStr">
+      <c r="H120" s="4" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
       </c>
-      <c r="H120" s="4" t="inlineStr">
+      <c r="I120" s="4" t="inlineStr">
         <is>
           <t>77% (17/22)</t>
         </is>
@@ -3946,29 +4549,34 @@
     </row>
     <row r="121">
       <c r="A121" s="3" t="n"/>
-      <c r="B121" s="3" t="inlineStr">
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
         <is>
           <t>doordash</t>
         </is>
       </c>
-      <c r="C121" s="3" t="inlineStr">
+      <c r="D121" s="3" t="inlineStr">
         <is>
           <t>to-event</t>
         </is>
       </c>
-      <c r="D121" s="4" t="n">
+      <c r="E121" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E121" s="3" t="n"/>
-      <c r="F121" s="4" t="n">
+      <c r="F121" s="3" t="n"/>
+      <c r="G121" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G121" s="4" t="inlineStr">
+      <c r="H121" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H121" s="4" t="inlineStr">
+      <c r="I121" s="4" t="inlineStr">
         <is>
           <t>40% (2/5)</t>
         </is>
@@ -3976,25 +4584,30 @@
     </row>
     <row r="122">
       <c r="A122" s="3" t="n"/>
-      <c r="B122" s="3" t="inlineStr">
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
         <is>
           <t>samsclub</t>
         </is>
       </c>
-      <c r="C122" s="3" t="inlineStr">
+      <c r="D122" s="3" t="inlineStr">
         <is>
           <t>auto-task-controller</t>
         </is>
       </c>
-      <c r="D122" s="4" t="n">
+      <c r="E122" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E122" s="3" t="n"/>
-      <c r="F122" s="4" t="n">
+      <c r="F122" s="3" t="n"/>
+      <c r="G122" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G122" s="4" t="n"/>
-      <c r="H122" s="4" t="inlineStr">
+      <c r="H122" s="4" t="n"/>
+      <c r="I122" s="4" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -4002,29 +4615,34 @@
     </row>
     <row r="123">
       <c r="A123" s="3" t="n"/>
-      <c r="B123" s="3" t="inlineStr">
+      <c r="B123" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
         <is>
           <t>samsclub</t>
         </is>
       </c>
-      <c r="C123" s="3" t="inlineStr">
+      <c r="D123" s="3" t="inlineStr">
         <is>
           <t>config-controller</t>
         </is>
       </c>
-      <c r="D123" s="4" t="n">
+      <c r="E123" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E123" s="3" t="n"/>
-      <c r="F123" s="4" t="n">
+      <c r="F123" s="3" t="n"/>
+      <c r="G123" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G123" s="4" t="inlineStr">
+      <c r="H123" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H123" s="4" t="inlineStr">
+      <c r="I123" s="4" t="inlineStr">
         <is>
           <t>70% (7/10)</t>
         </is>
@@ -4032,25 +4650,30 @@
     </row>
     <row r="124">
       <c r="A124" s="3" t="n"/>
-      <c r="B124" s="3" t="inlineStr">
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
         <is>
           <t>samsclub</t>
         </is>
       </c>
-      <c r="C124" s="3" t="inlineStr">
+      <c r="D124" s="3" t="inlineStr">
         <is>
           <t>data-impact-controller</t>
         </is>
       </c>
-      <c r="D124" s="4" t="n">
+      <c r="E124" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E124" s="3" t="n"/>
-      <c r="F124" s="4" t="n">
+      <c r="F124" s="3" t="n"/>
+      <c r="G124" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G124" s="4" t="n"/>
-      <c r="H124" s="4" t="inlineStr">
+      <c r="H124" s="4" t="n"/>
+      <c r="I124" s="4" t="inlineStr">
         <is>
           <t>0% (0/5)</t>
         </is>
@@ -4058,29 +4681,34 @@
     </row>
     <row r="125">
       <c r="A125" s="3" t="n"/>
-      <c r="B125" s="3" t="inlineStr">
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
         <is>
           <t>samsclub</t>
         </is>
       </c>
-      <c r="C125" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D125" s="4" t="n">
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="E125" s="3" t="n"/>
-      <c r="F125" s="4" t="n">
+      <c r="F125" s="3" t="n"/>
+      <c r="G125" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="G125" s="4" t="inlineStr">
+      <c r="H125" s="4" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="H125" s="4" t="inlineStr">
+      <c r="I125" s="4" t="inlineStr">
         <is>
           <t>75% (38/51)</t>
         </is>
@@ -4088,25 +4716,30 @@
     </row>
     <row r="126">
       <c r="A126" s="3" t="n"/>
-      <c r="B126" s="3" t="inlineStr">
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
         <is>
           <t>samsclub</t>
         </is>
       </c>
-      <c r="C126" s="3" t="inlineStr">
+      <c r="D126" s="3" t="inlineStr">
         <is>
           <t>feature-usage-controller</t>
         </is>
       </c>
-      <c r="D126" s="4" t="n">
+      <c r="E126" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E126" s="3" t="n"/>
-      <c r="F126" s="4" t="n">
+      <c r="F126" s="3" t="n"/>
+      <c r="G126" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G126" s="4" t="n"/>
-      <c r="H126" s="4" t="inlineStr">
+      <c r="H126" s="4" t="n"/>
+      <c r="I126" s="4" t="inlineStr">
         <is>
           <t>0% (0/2)</t>
         </is>
@@ -4114,25 +4747,30 @@
     </row>
     <row r="127">
       <c r="A127" s="3" t="n"/>
-      <c r="B127" s="3" t="inlineStr">
+      <c r="B127" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
         <is>
           <t>samsclub</t>
         </is>
       </c>
-      <c r="C127" s="3" t="inlineStr">
+      <c r="D127" s="3" t="inlineStr">
         <is>
           <t>health-controller</t>
         </is>
       </c>
-      <c r="D127" s="4" t="n">
+      <c r="E127" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E127" s="3" t="n"/>
-      <c r="F127" s="4" t="n">
+      <c r="F127" s="3" t="n"/>
+      <c r="G127" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G127" s="4" t="n"/>
-      <c r="H127" s="4" t="inlineStr">
+      <c r="H127" s="4" t="n"/>
+      <c r="I127" s="4" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -4140,29 +4778,34 @@
     </row>
     <row r="128">
       <c r="A128" s="3" t="n"/>
-      <c r="B128" s="3" t="inlineStr">
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
         <is>
           <t>samsclub</t>
         </is>
       </c>
-      <c r="C128" s="3" t="inlineStr">
+      <c r="D128" s="3" t="inlineStr">
         <is>
           <t>history-controller</t>
         </is>
       </c>
-      <c r="D128" s="4" t="n">
+      <c r="E128" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="E128" s="3" t="n"/>
-      <c r="F128" s="4" t="n">
+      <c r="F128" s="3" t="n"/>
+      <c r="G128" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G128" s="4" t="inlineStr">
+      <c r="H128" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H128" s="4" t="inlineStr">
+      <c r="I128" s="4" t="inlineStr">
         <is>
           <t>38% (10/26)</t>
         </is>
@@ -4170,49 +4813,59 @@
     </row>
     <row r="129">
       <c r="A129" s="3" t="n"/>
-      <c r="B129" s="3" t="inlineStr">
+      <c r="B129" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
         <is>
           <t>samsclub</t>
         </is>
       </c>
-      <c r="C129" s="3" t="inlineStr">
+      <c r="D129" s="3" t="inlineStr">
         <is>
           <t>migration-controller</t>
         </is>
       </c>
-      <c r="D129" s="4" t="n">
+      <c r="E129" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E129" s="3" t="n"/>
       <c r="F129" s="3" t="n"/>
       <c r="G129" s="3" t="n"/>
       <c r="H129" s="3" t="n"/>
+      <c r="I129" s="3" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n"/>
-      <c r="B130" s="3" t="inlineStr">
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
         <is>
           <t>samsclub</t>
         </is>
       </c>
-      <c r="C130" s="3" t="inlineStr">
+      <c r="D130" s="3" t="inlineStr">
         <is>
           <t>report-controller</t>
         </is>
       </c>
-      <c r="D130" s="4" t="n">
+      <c r="E130" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E130" s="3" t="n"/>
-      <c r="F130" s="4" t="n">
+      <c r="F130" s="3" t="n"/>
+      <c r="G130" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G130" s="4" t="inlineStr">
+      <c r="H130" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H130" s="4" t="inlineStr">
+      <c r="I130" s="4" t="inlineStr">
         <is>
           <t>8% (1/13)</t>
         </is>
@@ -4220,29 +4873,34 @@
     </row>
     <row r="131">
       <c r="A131" s="3" t="n"/>
-      <c r="B131" s="3" t="inlineStr">
+      <c r="B131" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
         <is>
           <t>samsclub</t>
         </is>
       </c>
-      <c r="C131" s="3" t="inlineStr">
+      <c r="D131" s="3" t="inlineStr">
         <is>
           <t>share-pass-controller</t>
         </is>
       </c>
-      <c r="D131" s="4" t="n">
+      <c r="E131" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E131" s="3" t="n"/>
-      <c r="F131" s="4" t="n">
+      <c r="F131" s="3" t="n"/>
+      <c r="G131" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G131" s="4" t="inlineStr">
+      <c r="H131" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H131" s="4" t="inlineStr">
+      <c r="I131" s="4" t="inlineStr">
         <is>
           <t>22% (2/9)</t>
         </is>
@@ -4250,29 +4908,34 @@
     </row>
     <row r="132">
       <c r="A132" s="3" t="n"/>
-      <c r="B132" s="3" t="inlineStr">
+      <c r="B132" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
         <is>
           <t>samsclub</t>
         </is>
       </c>
-      <c r="C132" s="3" t="inlineStr">
+      <c r="D132" s="3" t="inlineStr">
         <is>
           <t>template-controller</t>
         </is>
       </c>
-      <c r="D132" s="4" t="n">
+      <c r="E132" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="E132" s="3" t="n"/>
-      <c r="F132" s="4" t="n">
+      <c r="F132" s="3" t="n"/>
+      <c r="G132" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="G132" s="4" t="inlineStr">
+      <c r="H132" s="4" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
       </c>
-      <c r="H132" s="4" t="inlineStr">
+      <c r="I132" s="4" t="inlineStr">
         <is>
           <t>77% (17/22)</t>
         </is>
@@ -4280,29 +4943,34 @@
     </row>
     <row r="133">
       <c r="A133" s="3" t="n"/>
-      <c r="B133" s="3" t="inlineStr">
+      <c r="B133" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
         <is>
           <t>samsclub</t>
         </is>
       </c>
-      <c r="C133" s="3" t="inlineStr">
+      <c r="D133" s="3" t="inlineStr">
         <is>
           <t>to-event</t>
         </is>
       </c>
-      <c r="D133" s="4" t="n">
+      <c r="E133" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E133" s="3" t="n"/>
-      <c r="F133" s="4" t="n">
+      <c r="F133" s="3" t="n"/>
+      <c r="G133" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G133" s="4" t="inlineStr">
+      <c r="H133" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H133" s="4" t="inlineStr">
+      <c r="I133" s="4" t="inlineStr">
         <is>
           <t>40% (2/5)</t>
         </is>
@@ -4310,29 +4978,34 @@
     </row>
     <row r="134">
       <c r="A134" s="3" t="n"/>
-      <c r="B134" s="3" t="inlineStr">
+      <c r="B134" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
         <is>
           <t>bol</t>
         </is>
       </c>
-      <c r="C134" s="3" t="inlineStr">
+      <c r="D134" s="3" t="inlineStr">
         <is>
           <t>auto-task-controller</t>
         </is>
       </c>
-      <c r="D134" s="4" t="n">
+      <c r="E134" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E134" s="3" t="n"/>
-      <c r="F134" s="4" t="n">
+      <c r="F134" s="3" t="n"/>
+      <c r="G134" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G134" s="4" t="inlineStr">
+      <c r="H134" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H134" s="4" t="inlineStr">
+      <c r="I134" s="4" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -4340,29 +5013,34 @@
     </row>
     <row r="135">
       <c r="A135" s="3" t="n"/>
-      <c r="B135" s="3" t="inlineStr">
+      <c r="B135" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
         <is>
           <t>bol</t>
         </is>
       </c>
-      <c r="C135" s="3" t="inlineStr">
+      <c r="D135" s="3" t="inlineStr">
         <is>
           <t>config-controller</t>
         </is>
       </c>
-      <c r="D135" s="4" t="n">
+      <c r="E135" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E135" s="3" t="n"/>
-      <c r="F135" s="4" t="n">
+      <c r="F135" s="3" t="n"/>
+      <c r="G135" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G135" s="4" t="inlineStr">
+      <c r="H135" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H135" s="4" t="inlineStr">
+      <c r="I135" s="4" t="inlineStr">
         <is>
           <t>70% (7/10)</t>
         </is>
@@ -4370,29 +5048,34 @@
     </row>
     <row r="136">
       <c r="A136" s="3" t="n"/>
-      <c r="B136" s="3" t="inlineStr">
+      <c r="B136" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
         <is>
           <t>bol</t>
         </is>
       </c>
-      <c r="C136" s="3" t="inlineStr">
+      <c r="D136" s="3" t="inlineStr">
         <is>
           <t>data-impact-controller</t>
         </is>
       </c>
-      <c r="D136" s="4" t="n">
+      <c r="E136" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E136" s="3" t="n"/>
-      <c r="F136" s="4" t="n">
+      <c r="F136" s="3" t="n"/>
+      <c r="G136" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G136" s="4" t="inlineStr">
+      <c r="H136" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H136" s="4" t="inlineStr">
+      <c r="I136" s="4" t="inlineStr">
         <is>
           <t>40% (2/5)</t>
         </is>
@@ -4400,29 +5083,34 @@
     </row>
     <row r="137">
       <c r="A137" s="3" t="n"/>
-      <c r="B137" s="3" t="inlineStr">
+      <c r="B137" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
         <is>
           <t>bol</t>
         </is>
       </c>
-      <c r="C137" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D137" s="4" t="n">
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="E137" s="3" t="n"/>
-      <c r="F137" s="4" t="n">
+      <c r="F137" s="3" t="n"/>
+      <c r="G137" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="G137" s="4" t="inlineStr">
+      <c r="H137" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H137" s="4" t="inlineStr">
+      <c r="I137" s="4" t="inlineStr">
         <is>
           <t>29% (15/51)</t>
         </is>
@@ -4430,29 +5118,34 @@
     </row>
     <row r="138">
       <c r="A138" s="3" t="n"/>
-      <c r="B138" s="3" t="inlineStr">
+      <c r="B138" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
         <is>
           <t>bol</t>
         </is>
       </c>
-      <c r="C138" s="3" t="inlineStr">
+      <c r="D138" s="3" t="inlineStr">
         <is>
           <t>feature-usage-controller</t>
         </is>
       </c>
-      <c r="D138" s="4" t="n">
+      <c r="E138" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E138" s="3" t="n"/>
-      <c r="F138" s="4" t="n">
+      <c r="F138" s="3" t="n"/>
+      <c r="G138" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G138" s="4" t="inlineStr">
+      <c r="H138" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H138" s="4" t="inlineStr">
+      <c r="I138" s="4" t="inlineStr">
         <is>
           <t>0% (0/2)</t>
         </is>
@@ -4460,29 +5153,34 @@
     </row>
     <row r="139">
       <c r="A139" s="3" t="n"/>
-      <c r="B139" s="3" t="inlineStr">
+      <c r="B139" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
         <is>
           <t>bol</t>
         </is>
       </c>
-      <c r="C139" s="3" t="inlineStr">
+      <c r="D139" s="3" t="inlineStr">
         <is>
           <t>health-controller</t>
         </is>
       </c>
-      <c r="D139" s="4" t="n">
+      <c r="E139" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E139" s="3" t="n"/>
-      <c r="F139" s="4" t="n">
+      <c r="F139" s="3" t="n"/>
+      <c r="G139" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G139" s="4" t="inlineStr">
+      <c r="H139" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H139" s="4" t="inlineStr">
+      <c r="I139" s="4" t="inlineStr">
         <is>
           <t>100% (1/1)</t>
         </is>
@@ -4490,29 +5188,34 @@
     </row>
     <row r="140">
       <c r="A140" s="3" t="n"/>
-      <c r="B140" s="3" t="inlineStr">
+      <c r="B140" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
         <is>
           <t>bol</t>
         </is>
       </c>
-      <c r="C140" s="3" t="inlineStr">
+      <c r="D140" s="3" t="inlineStr">
         <is>
           <t>history-controller</t>
         </is>
       </c>
-      <c r="D140" s="4" t="n">
+      <c r="E140" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="E140" s="3" t="n"/>
-      <c r="F140" s="4" t="n">
+      <c r="F140" s="3" t="n"/>
+      <c r="G140" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="G140" s="4" t="inlineStr">
+      <c r="H140" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H140" s="4" t="inlineStr">
+      <c r="I140" s="4" t="inlineStr">
         <is>
           <t>62% (16/26)</t>
         </is>
@@ -4520,49 +5223,59 @@
     </row>
     <row r="141">
       <c r="A141" s="3" t="n"/>
-      <c r="B141" s="3" t="inlineStr">
+      <c r="B141" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
         <is>
           <t>bol</t>
         </is>
       </c>
-      <c r="C141" s="3" t="inlineStr">
+      <c r="D141" s="3" t="inlineStr">
         <is>
           <t>migration-controller</t>
         </is>
       </c>
-      <c r="D141" s="4" t="n">
+      <c r="E141" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E141" s="3" t="n"/>
       <c r="F141" s="3" t="n"/>
       <c r="G141" s="3" t="n"/>
       <c r="H141" s="3" t="n"/>
+      <c r="I141" s="3" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n"/>
-      <c r="B142" s="3" t="inlineStr">
+      <c r="B142" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
         <is>
           <t>bol</t>
         </is>
       </c>
-      <c r="C142" s="3" t="inlineStr">
+      <c r="D142" s="3" t="inlineStr">
         <is>
           <t>report-controller</t>
         </is>
       </c>
-      <c r="D142" s="4" t="n">
+      <c r="E142" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E142" s="3" t="n"/>
-      <c r="F142" s="4" t="n">
+      <c r="F142" s="3" t="n"/>
+      <c r="G142" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G142" s="4" t="inlineStr">
+      <c r="H142" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H142" s="4" t="inlineStr">
+      <c r="I142" s="4" t="inlineStr">
         <is>
           <t>23% (3/13)</t>
         </is>
@@ -4570,29 +5283,34 @@
     </row>
     <row r="143">
       <c r="A143" s="3" t="n"/>
-      <c r="B143" s="3" t="inlineStr">
+      <c r="B143" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
         <is>
           <t>bol</t>
         </is>
       </c>
-      <c r="C143" s="3" t="inlineStr">
+      <c r="D143" s="3" t="inlineStr">
         <is>
           <t>share-pass-controller</t>
         </is>
       </c>
-      <c r="D143" s="4" t="n">
+      <c r="E143" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E143" s="3" t="n"/>
-      <c r="F143" s="4" t="n">
+      <c r="F143" s="3" t="n"/>
+      <c r="G143" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G143" s="4" t="inlineStr">
+      <c r="H143" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H143" s="4" t="inlineStr">
+      <c r="I143" s="4" t="inlineStr">
         <is>
           <t>22% (2/9)</t>
         </is>
@@ -4600,29 +5318,34 @@
     </row>
     <row r="144">
       <c r="A144" s="3" t="n"/>
-      <c r="B144" s="3" t="inlineStr">
+      <c r="B144" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
         <is>
           <t>bol</t>
         </is>
       </c>
-      <c r="C144" s="3" t="inlineStr">
+      <c r="D144" s="3" t="inlineStr">
         <is>
           <t>template-controller</t>
         </is>
       </c>
-      <c r="D144" s="4" t="n">
+      <c r="E144" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="E144" s="3" t="n"/>
-      <c r="F144" s="4" t="n">
+      <c r="F144" s="3" t="n"/>
+      <c r="G144" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="G144" s="4" t="inlineStr">
+      <c r="H144" s="4" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
       </c>
-      <c r="H144" s="4" t="inlineStr">
+      <c r="I144" s="4" t="inlineStr">
         <is>
           <t>77% (17/22)</t>
         </is>
@@ -4630,29 +5353,34 @@
     </row>
     <row r="145">
       <c r="A145" s="3" t="n"/>
-      <c r="B145" s="3" t="inlineStr">
+      <c r="B145" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
         <is>
           <t>bol</t>
         </is>
       </c>
-      <c r="C145" s="3" t="inlineStr">
+      <c r="D145" s="3" t="inlineStr">
         <is>
           <t>to-event</t>
         </is>
       </c>
-      <c r="D145" s="4" t="n">
+      <c r="E145" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E145" s="3" t="n"/>
-      <c r="F145" s="4" t="n">
+      <c r="F145" s="3" t="n"/>
+      <c r="G145" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G145" s="4" t="inlineStr">
+      <c r="H145" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H145" s="4" t="inlineStr">
+      <c r="I145" s="4" t="inlineStr">
         <is>
           <t>40% (2/5)</t>
         </is>
@@ -4660,25 +5388,30 @@
     </row>
     <row r="146">
       <c r="A146" s="3" t="n"/>
-      <c r="B146" s="3" t="inlineStr">
+      <c r="B146" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
         <is>
           <t>mercado</t>
         </is>
       </c>
-      <c r="C146" s="3" t="inlineStr">
+      <c r="D146" s="3" t="inlineStr">
         <is>
           <t>auto-task-controller</t>
         </is>
       </c>
-      <c r="D146" s="4" t="n">
+      <c r="E146" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E146" s="3" t="n"/>
-      <c r="F146" s="3" t="n">
+      <c r="F146" s="3" t="n"/>
+      <c r="G146" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G146" s="3" t="n"/>
-      <c r="H146" s="3" t="inlineStr">
+      <c r="H146" s="3" t="n"/>
+      <c r="I146" s="3" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -4686,29 +5419,34 @@
     </row>
     <row r="147">
       <c r="A147" s="3" t="n"/>
-      <c r="B147" s="3" t="inlineStr">
+      <c r="B147" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
         <is>
           <t>mercado</t>
         </is>
       </c>
-      <c r="C147" s="3" t="inlineStr">
+      <c r="D147" s="3" t="inlineStr">
         <is>
           <t>config-controller</t>
         </is>
       </c>
-      <c r="D147" s="4" t="n">
+      <c r="E147" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E147" s="3" t="n"/>
-      <c r="F147" s="4" t="n">
+      <c r="F147" s="3" t="n"/>
+      <c r="G147" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G147" s="4" t="inlineStr">
+      <c r="H147" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H147" s="4" t="inlineStr">
+      <c r="I147" s="4" t="inlineStr">
         <is>
           <t>80% (8/10)</t>
         </is>
@@ -4716,29 +5454,34 @@
     </row>
     <row r="148">
       <c r="A148" s="3" t="n"/>
-      <c r="B148" s="3" t="inlineStr">
+      <c r="B148" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
         <is>
           <t>mercado</t>
         </is>
       </c>
-      <c r="C148" s="3" t="inlineStr">
+      <c r="D148" s="3" t="inlineStr">
         <is>
           <t>data-impact-controller</t>
         </is>
       </c>
-      <c r="D148" s="4" t="n">
+      <c r="E148" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E148" s="3" t="n"/>
-      <c r="F148" s="4" t="n">
+      <c r="F148" s="3" t="n"/>
+      <c r="G148" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G148" s="4" t="inlineStr">
+      <c r="H148" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="H148" s="4" t="inlineStr">
+      <c r="I148" s="4" t="inlineStr">
         <is>
           <t>40% (2/5)</t>
         </is>
@@ -4746,29 +5489,34 @@
     </row>
     <row r="149">
       <c r="A149" s="3" t="n"/>
-      <c r="B149" s="3" t="inlineStr">
+      <c r="B149" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
         <is>
           <t>mercado</t>
         </is>
       </c>
-      <c r="C149" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D149" s="4" t="n">
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="E149" s="3" t="n"/>
-      <c r="F149" s="4" t="n">
+      <c r="F149" s="3" t="n"/>
+      <c r="G149" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G149" s="4" t="inlineStr">
+      <c r="H149" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H149" s="4" t="inlineStr">
+      <c r="I149" s="4" t="inlineStr">
         <is>
           <t>12% (6/51)</t>
         </is>
@@ -4776,25 +5524,30 @@
     </row>
     <row r="150">
       <c r="A150" s="3" t="n"/>
-      <c r="B150" s="3" t="inlineStr">
+      <c r="B150" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
         <is>
           <t>mercado</t>
         </is>
       </c>
-      <c r="C150" s="3" t="inlineStr">
+      <c r="D150" s="3" t="inlineStr">
         <is>
           <t>feature-usage-controller</t>
         </is>
       </c>
-      <c r="D150" s="4" t="n">
+      <c r="E150" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E150" s="3" t="n"/>
-      <c r="F150" s="3" t="n">
+      <c r="F150" s="3" t="n"/>
+      <c r="G150" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G150" s="3" t="n"/>
-      <c r="H150" s="3" t="inlineStr">
+      <c r="H150" s="3" t="n"/>
+      <c r="I150" s="3" t="inlineStr">
         <is>
           <t>0% (0/2)</t>
         </is>
@@ -4802,25 +5555,30 @@
     </row>
     <row r="151">
       <c r="A151" s="3" t="n"/>
-      <c r="B151" s="3" t="inlineStr">
+      <c r="B151" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
         <is>
           <t>mercado</t>
         </is>
       </c>
-      <c r="C151" s="3" t="inlineStr">
+      <c r="D151" s="3" t="inlineStr">
         <is>
           <t>health-controller</t>
         </is>
       </c>
-      <c r="D151" s="4" t="n">
+      <c r="E151" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E151" s="3" t="n"/>
-      <c r="F151" s="3" t="n">
+      <c r="F151" s="3" t="n"/>
+      <c r="G151" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G151" s="3" t="n"/>
-      <c r="H151" s="3" t="inlineStr">
+      <c r="H151" s="3" t="n"/>
+      <c r="I151" s="3" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -4828,29 +5586,34 @@
     </row>
     <row r="152">
       <c r="A152" s="3" t="n"/>
-      <c r="B152" s="3" t="inlineStr">
+      <c r="B152" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
         <is>
           <t>mercado</t>
         </is>
       </c>
-      <c r="C152" s="3" t="inlineStr">
+      <c r="D152" s="3" t="inlineStr">
         <is>
           <t>history-controller</t>
         </is>
       </c>
-      <c r="D152" s="4" t="n">
+      <c r="E152" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="E152" s="3" t="n"/>
-      <c r="F152" s="4" t="n">
+      <c r="F152" s="3" t="n"/>
+      <c r="G152" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="G152" s="4" t="inlineStr">
+      <c r="H152" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H152" s="4" t="inlineStr">
+      <c r="I152" s="4" t="inlineStr">
         <is>
           <t>54% (14/26)</t>
         </is>
@@ -4858,49 +5621,59 @@
     </row>
     <row r="153">
       <c r="A153" s="3" t="n"/>
-      <c r="B153" s="3" t="inlineStr">
+      <c r="B153" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
         <is>
           <t>mercado</t>
         </is>
       </c>
-      <c r="C153" s="3" t="inlineStr">
+      <c r="D153" s="3" t="inlineStr">
         <is>
           <t>migration-controller</t>
         </is>
       </c>
-      <c r="D153" s="4" t="n">
+      <c r="E153" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E153" s="3" t="n"/>
       <c r="F153" s="3" t="n"/>
       <c r="G153" s="3" t="n"/>
       <c r="H153" s="3" t="n"/>
+      <c r="I153" s="3" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n"/>
-      <c r="B154" s="3" t="inlineStr">
+      <c r="B154" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
         <is>
           <t>mercado</t>
         </is>
       </c>
-      <c r="C154" s="3" t="inlineStr">
+      <c r="D154" s="3" t="inlineStr">
         <is>
           <t>report-controller</t>
         </is>
       </c>
-      <c r="D154" s="4" t="n">
+      <c r="E154" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E154" s="3" t="n"/>
-      <c r="F154" s="4" t="n">
+      <c r="F154" s="3" t="n"/>
+      <c r="G154" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G154" s="4" t="inlineStr">
+      <c r="H154" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H154" s="4" t="inlineStr">
+      <c r="I154" s="4" t="inlineStr">
         <is>
           <t>23% (3/13)</t>
         </is>
@@ -4908,29 +5681,34 @@
     </row>
     <row r="155">
       <c r="A155" s="3" t="n"/>
-      <c r="B155" s="3" t="inlineStr">
+      <c r="B155" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
         <is>
           <t>mercado</t>
         </is>
       </c>
-      <c r="C155" s="3" t="inlineStr">
+      <c r="D155" s="3" t="inlineStr">
         <is>
           <t>share-pass-controller</t>
         </is>
       </c>
-      <c r="D155" s="4" t="n">
+      <c r="E155" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E155" s="3" t="n"/>
-      <c r="F155" s="4" t="n">
+      <c r="F155" s="3" t="n"/>
+      <c r="G155" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G155" s="4" t="inlineStr">
+      <c r="H155" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H155" s="4" t="inlineStr">
+      <c r="I155" s="4" t="inlineStr">
         <is>
           <t>22% (2/9)</t>
         </is>
@@ -4938,29 +5716,34 @@
     </row>
     <row r="156">
       <c r="A156" s="3" t="n"/>
-      <c r="B156" s="3" t="inlineStr">
+      <c r="B156" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
         <is>
           <t>mercado</t>
         </is>
       </c>
-      <c r="C156" s="3" t="inlineStr">
+      <c r="D156" s="3" t="inlineStr">
         <is>
           <t>template-controller</t>
         </is>
       </c>
-      <c r="D156" s="4" t="n">
+      <c r="E156" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="E156" s="3" t="n"/>
-      <c r="F156" s="4" t="n">
+      <c r="F156" s="3" t="n"/>
+      <c r="G156" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G156" s="4" t="inlineStr">
+      <c r="H156" s="4" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
       </c>
-      <c r="H156" s="4" t="inlineStr">
+      <c r="I156" s="4" t="inlineStr">
         <is>
           <t>77% (17/22)</t>
         </is>
@@ -4968,29 +5751,34 @@
     </row>
     <row r="157">
       <c r="A157" s="3" t="n"/>
-      <c r="B157" s="3" t="inlineStr">
+      <c r="B157" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
         <is>
           <t>mercado</t>
         </is>
       </c>
-      <c r="C157" s="3" t="inlineStr">
+      <c r="D157" s="3" t="inlineStr">
         <is>
           <t>to-event</t>
         </is>
       </c>
-      <c r="D157" s="4" t="n">
+      <c r="E157" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E157" s="3" t="n"/>
-      <c r="F157" s="4" t="n">
+      <c r="F157" s="3" t="n"/>
+      <c r="G157" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G157" s="4" t="inlineStr">
+      <c r="H157" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H157" s="4" t="inlineStr">
+      <c r="I157" s="4" t="inlineStr">
         <is>
           <t>40% (2/5)</t>
         </is>
@@ -4998,25 +5786,30 @@
     </row>
     <row r="158">
       <c r="A158" s="3" t="n"/>
-      <c r="B158" s="3" t="inlineStr">
+      <c r="B158" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
         <is>
           <t>ebay</t>
         </is>
       </c>
-      <c r="C158" s="3" t="inlineStr">
+      <c r="D158" s="3" t="inlineStr">
         <is>
           <t>auto-task-controller</t>
         </is>
       </c>
-      <c r="D158" s="4" t="n">
+      <c r="E158" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E158" s="3" t="n"/>
-      <c r="F158" s="3" t="n">
+      <c r="F158" s="3" t="n"/>
+      <c r="G158" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G158" s="3" t="n"/>
-      <c r="H158" s="3" t="inlineStr">
+      <c r="H158" s="3" t="n"/>
+      <c r="I158" s="3" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -5024,29 +5817,34 @@
     </row>
     <row r="159">
       <c r="A159" s="3" t="n"/>
-      <c r="B159" s="3" t="inlineStr">
+      <c r="B159" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
         <is>
           <t>ebay</t>
         </is>
       </c>
-      <c r="C159" s="3" t="inlineStr">
+      <c r="D159" s="3" t="inlineStr">
         <is>
           <t>config-controller</t>
         </is>
       </c>
-      <c r="D159" s="4" t="n">
+      <c r="E159" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E159" s="3" t="n"/>
-      <c r="F159" s="4" t="n">
+      <c r="F159" s="3" t="n"/>
+      <c r="G159" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G159" s="4" t="inlineStr">
+      <c r="H159" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H159" s="4" t="inlineStr">
+      <c r="I159" s="4" t="inlineStr">
         <is>
           <t>80% (8/10)</t>
         </is>
@@ -5054,29 +5852,34 @@
     </row>
     <row r="160">
       <c r="A160" s="3" t="n"/>
-      <c r="B160" s="3" t="inlineStr">
+      <c r="B160" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
         <is>
           <t>ebay</t>
         </is>
       </c>
-      <c r="C160" s="3" t="inlineStr">
+      <c r="D160" s="3" t="inlineStr">
         <is>
           <t>data-impact-controller</t>
         </is>
       </c>
-      <c r="D160" s="4" t="n">
+      <c r="E160" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E160" s="3" t="n"/>
-      <c r="F160" s="4" t="n">
+      <c r="F160" s="3" t="n"/>
+      <c r="G160" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G160" s="4" t="inlineStr">
+      <c r="H160" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H160" s="4" t="inlineStr">
+      <c r="I160" s="4" t="inlineStr">
         <is>
           <t>40% (2/5)</t>
         </is>
@@ -5084,29 +5887,34 @@
     </row>
     <row r="161">
       <c r="A161" s="3" t="n"/>
-      <c r="B161" s="3" t="inlineStr">
+      <c r="B161" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
         <is>
           <t>ebay</t>
         </is>
       </c>
-      <c r="C161" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D161" s="4" t="n">
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="E161" s="3" t="n"/>
-      <c r="F161" s="4" t="n">
+      <c r="F161" s="3" t="n"/>
+      <c r="G161" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="G161" s="4" t="inlineStr">
+      <c r="H161" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H161" s="4" t="inlineStr">
+      <c r="I161" s="4" t="inlineStr">
         <is>
           <t>35% (18/51)</t>
         </is>
@@ -5114,25 +5922,30 @@
     </row>
     <row r="162">
       <c r="A162" s="3" t="n"/>
-      <c r="B162" s="3" t="inlineStr">
+      <c r="B162" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
         <is>
           <t>ebay</t>
         </is>
       </c>
-      <c r="C162" s="3" t="inlineStr">
+      <c r="D162" s="3" t="inlineStr">
         <is>
           <t>feature-usage-controller</t>
         </is>
       </c>
-      <c r="D162" s="4" t="n">
+      <c r="E162" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E162" s="3" t="n"/>
-      <c r="F162" s="3" t="n">
+      <c r="F162" s="3" t="n"/>
+      <c r="G162" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G162" s="3" t="n"/>
-      <c r="H162" s="3" t="inlineStr">
+      <c r="H162" s="3" t="n"/>
+      <c r="I162" s="3" t="inlineStr">
         <is>
           <t>0% (0/2)</t>
         </is>
@@ -5140,25 +5953,30 @@
     </row>
     <row r="163">
       <c r="A163" s="3" t="n"/>
-      <c r="B163" s="3" t="inlineStr">
+      <c r="B163" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
         <is>
           <t>ebay</t>
         </is>
       </c>
-      <c r="C163" s="3" t="inlineStr">
+      <c r="D163" s="3" t="inlineStr">
         <is>
           <t>health-controller</t>
         </is>
       </c>
-      <c r="D163" s="4" t="n">
+      <c r="E163" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E163" s="3" t="n"/>
-      <c r="F163" s="3" t="n">
+      <c r="F163" s="3" t="n"/>
+      <c r="G163" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G163" s="3" t="n"/>
-      <c r="H163" s="3" t="inlineStr">
+      <c r="H163" s="3" t="n"/>
+      <c r="I163" s="3" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -5166,29 +5984,34 @@
     </row>
     <row r="164">
       <c r="A164" s="3" t="n"/>
-      <c r="B164" s="3" t="inlineStr">
+      <c r="B164" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
         <is>
           <t>ebay</t>
         </is>
       </c>
-      <c r="C164" s="3" t="inlineStr">
+      <c r="D164" s="3" t="inlineStr">
         <is>
           <t>history-controller</t>
         </is>
       </c>
-      <c r="D164" s="4" t="n">
+      <c r="E164" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="E164" s="3" t="n"/>
-      <c r="F164" s="4" t="n">
+      <c r="F164" s="3" t="n"/>
+      <c r="G164" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="G164" s="4" t="inlineStr">
+      <c r="H164" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H164" s="4" t="inlineStr">
+      <c r="I164" s="4" t="inlineStr">
         <is>
           <t>54% (14/26)</t>
         </is>
@@ -5196,49 +6019,59 @@
     </row>
     <row r="165">
       <c r="A165" s="3" t="n"/>
-      <c r="B165" s="3" t="inlineStr">
+      <c r="B165" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
         <is>
           <t>ebay</t>
         </is>
       </c>
-      <c r="C165" s="3" t="inlineStr">
+      <c r="D165" s="3" t="inlineStr">
         <is>
           <t>migration-controller</t>
         </is>
       </c>
-      <c r="D165" s="4" t="n">
+      <c r="E165" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E165" s="3" t="n"/>
       <c r="F165" s="3" t="n"/>
       <c r="G165" s="3" t="n"/>
       <c r="H165" s="3" t="n"/>
+      <c r="I165" s="3" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n"/>
-      <c r="B166" s="3" t="inlineStr">
+      <c r="B166" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
         <is>
           <t>ebay</t>
         </is>
       </c>
-      <c r="C166" s="3" t="inlineStr">
+      <c r="D166" s="3" t="inlineStr">
         <is>
           <t>report-controller</t>
         </is>
       </c>
-      <c r="D166" s="4" t="n">
+      <c r="E166" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E166" s="3" t="n"/>
-      <c r="F166" s="4" t="n">
+      <c r="F166" s="3" t="n"/>
+      <c r="G166" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G166" s="4" t="inlineStr">
+      <c r="H166" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H166" s="4" t="inlineStr">
+      <c r="I166" s="4" t="inlineStr">
         <is>
           <t>23% (3/13)</t>
         </is>
@@ -5246,29 +6079,34 @@
     </row>
     <row r="167">
       <c r="A167" s="3" t="n"/>
-      <c r="B167" s="3" t="inlineStr">
+      <c r="B167" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
         <is>
           <t>ebay</t>
         </is>
       </c>
-      <c r="C167" s="3" t="inlineStr">
+      <c r="D167" s="3" t="inlineStr">
         <is>
           <t>share-pass-controller</t>
         </is>
       </c>
-      <c r="D167" s="4" t="n">
+      <c r="E167" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E167" s="3" t="n"/>
-      <c r="F167" s="4" t="n">
+      <c r="F167" s="3" t="n"/>
+      <c r="G167" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G167" s="4" t="inlineStr">
+      <c r="H167" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H167" s="4" t="inlineStr">
+      <c r="I167" s="4" t="inlineStr">
         <is>
           <t>22% (2/9)</t>
         </is>
@@ -5276,29 +6114,34 @@
     </row>
     <row r="168">
       <c r="A168" s="3" t="n"/>
-      <c r="B168" s="3" t="inlineStr">
+      <c r="B168" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
         <is>
           <t>ebay</t>
         </is>
       </c>
-      <c r="C168" s="3" t="inlineStr">
+      <c r="D168" s="3" t="inlineStr">
         <is>
           <t>template-controller</t>
         </is>
       </c>
-      <c r="D168" s="4" t="n">
+      <c r="E168" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="E168" s="3" t="n"/>
-      <c r="F168" s="4" t="n">
+      <c r="F168" s="3" t="n"/>
+      <c r="G168" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="G168" s="4" t="inlineStr">
+      <c r="H168" s="4" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
       </c>
-      <c r="H168" s="4" t="inlineStr">
+      <c r="I168" s="4" t="inlineStr">
         <is>
           <t>77% (17/22)</t>
         </is>
@@ -5306,29 +6149,34 @@
     </row>
     <row r="169">
       <c r="A169" s="3" t="n"/>
-      <c r="B169" s="3" t="inlineStr">
+      <c r="B169" s="9" t="inlineStr">
+        <is>
+          <t>RuleApi</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
         <is>
           <t>ebay</t>
         </is>
       </c>
-      <c r="C169" s="3" t="inlineStr">
+      <c r="D169" s="3" t="inlineStr">
         <is>
           <t>to-event</t>
         </is>
       </c>
-      <c r="D169" s="4" t="n">
+      <c r="E169" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E169" s="3" t="n"/>
-      <c r="F169" s="4" t="n">
+      <c r="F169" s="3" t="n"/>
+      <c r="G169" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G169" s="4" t="inlineStr">
+      <c r="H169" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H169" s="4" t="inlineStr">
+      <c r="I169" s="4" t="inlineStr">
         <is>
           <t>40% (2/5)</t>
         </is>
@@ -5345,7 +6193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2068"/>
+  <dimension ref="A1:H2068"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5355,6 +6203,7 @@
     <col width="45" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5391,6 +6240,11 @@
       <c r="G1" s="6" t="inlineStr">
         <is>
           <t>场景覆盖</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>

--- a/single-api/services/rule-api/swagger_modules.xlsx
+++ b/single-api/services/rule-api/swagger_modules.xlsx
@@ -92,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -118,6 +118,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -484,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I169"/>
+  <dimension ref="A1:J169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -543,6 +546,11 @@
           <t>接口覆盖率</t>
         </is>
       </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>模块路径</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -582,6 +590,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\amazon\us\auto-task-controller</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n"/>
@@ -617,6 +630,11 @@
           <t>100% (10/10)</t>
         </is>
       </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\amazon\us\config-controller</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
@@ -652,6 +670,11 @@
           <t>100% (5/5)</t>
         </is>
       </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\amazon\us\data-impact-controller</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
@@ -687,6 +710,11 @@
           <t>55% (28/51)</t>
         </is>
       </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\amazon\us\definition-controller</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n"/>
@@ -722,6 +750,11 @@
           <t>100% (2/2)</t>
         </is>
       </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\amazon\us\feature-usage-controller</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n"/>
@@ -757,6 +790,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\amazon\us\health-controller</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
@@ -790,6 +828,11 @@
       <c r="I8" s="4" t="inlineStr">
         <is>
           <t>100% (26/26)</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\amazon\us\history-controller</t>
         </is>
       </c>
     </row>
@@ -817,6 +860,11 @@
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="n"/>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\amazon\us\migration-controller</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n"/>
@@ -852,6 +900,11 @@
           <t>85% (11/13)</t>
         </is>
       </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\amazon\us\report-controller</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
@@ -887,6 +940,11 @@
           <t>100% (9/9)</t>
         </is>
       </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\amazon\us\share-pass-controller</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n"/>
@@ -922,6 +980,11 @@
           <t>73% (16/22)</t>
         </is>
       </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\amazon\us\template-controller</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n"/>
@@ -957,6 +1020,11 @@
           <t>80% (4/5)</t>
         </is>
       </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\amazon\us\to-event</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
@@ -992,6 +1060,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\tiktok\us\auto-task-controller</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n"/>
@@ -1027,6 +1100,11 @@
           <t>100% (10/10)</t>
         </is>
       </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\tiktok\us\config-controller</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n"/>
@@ -1062,6 +1140,11 @@
           <t>100% (5/5)</t>
         </is>
       </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\tiktok\us\data-impact-controller</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
@@ -1097,6 +1180,11 @@
           <t>29% (15/51)</t>
         </is>
       </c>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\tiktok\us\definition-controller</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n"/>
@@ -1132,6 +1220,11 @@
           <t>100% (2/2)</t>
         </is>
       </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\tiktok\us\feature-usage-controller</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n"/>
@@ -1167,6 +1260,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="J19" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\tiktok\us\health-controller</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n"/>
@@ -1200,6 +1298,11 @@
       <c r="I20" s="4" t="inlineStr">
         <is>
           <t>96% (25/26)</t>
+        </is>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\tiktok\us\history-controller</t>
         </is>
       </c>
     </row>
@@ -1227,6 +1330,11 @@
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="4" t="n"/>
       <c r="I21" s="4" t="n"/>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\tiktok\us\migration-controller</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n"/>
@@ -1262,6 +1370,11 @@
           <t>100% (13/13)</t>
         </is>
       </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\tiktok\us\report-controller</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
@@ -1297,6 +1410,11 @@
           <t>100% (9/9)</t>
         </is>
       </c>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\tiktok\us\share-pass-controller</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n"/>
@@ -1332,6 +1450,11 @@
           <t>73% (16/22)</t>
         </is>
       </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\tiktok\us\template-controller</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n"/>
@@ -1367,6 +1490,11 @@
           <t>100% (5/5)</t>
         </is>
       </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\tiktok\us\to-event</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n"/>
@@ -1402,6 +1530,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\walmart\us\auto-task-controller</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n"/>
@@ -1437,6 +1570,11 @@
           <t>100% (10/10)</t>
         </is>
       </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\walmart\us\config-controller</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n"/>
@@ -1470,6 +1608,11 @@
       <c r="I28" s="4" t="inlineStr">
         <is>
           <t>100% (5/5)</t>
+        </is>
+      </c>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\walmart\us\data-impact-controller</t>
         </is>
       </c>
     </row>
@@ -1497,6 +1640,11 @@
       <c r="G29" s="3" t="n"/>
       <c r="H29" s="3" t="n"/>
       <c r="I29" s="3" t="n"/>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\walmart\us\definition-controller</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n"/>
@@ -1532,6 +1680,11 @@
           <t>100% (2/2)</t>
         </is>
       </c>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\walmart\us\feature-usage-controller</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n"/>
@@ -1567,6 +1720,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\walmart\us\health-controller</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n"/>
@@ -1600,6 +1758,11 @@
       <c r="I32" s="4" t="inlineStr">
         <is>
           <t>100% (26/26)</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\walmart\us\history-controller</t>
         </is>
       </c>
     </row>
@@ -1627,6 +1790,11 @@
       <c r="G33" s="3" t="n"/>
       <c r="H33" s="3" t="n"/>
       <c r="I33" s="3" t="n"/>
+      <c r="J33" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\walmart\us\migration-controller</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n"/>
@@ -1662,6 +1830,11 @@
           <t>85% (11/13)</t>
         </is>
       </c>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\walmart\us\report-controller</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n"/>
@@ -1697,6 +1870,11 @@
           <t>100% (9/9)</t>
         </is>
       </c>
+      <c r="J35" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\walmart\us\share-pass-controller</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n"/>
@@ -1732,6 +1910,11 @@
           <t>73% (16/22)</t>
         </is>
       </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\walmart\us\template-controller</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n"/>
@@ -1767,6 +1950,11 @@
           <t>80% (4/5)</t>
         </is>
       </c>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\walmart\us\to-event</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n"/>
@@ -1802,6 +1990,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\instacart\us\auto-task-controller</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n"/>
@@ -1837,6 +2030,11 @@
           <t>90% (9/10)</t>
         </is>
       </c>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\instacart\us\config-controller</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n"/>
@@ -1872,6 +2070,11 @@
           <t>100% (5/5)</t>
         </is>
       </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\instacart\us\data-impact-controller</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n"/>
@@ -1907,6 +2110,11 @@
           <t>100% (51/51)</t>
         </is>
       </c>
+      <c r="J41" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\instacart\us\definition-controller</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n"/>
@@ -1942,6 +2150,11 @@
           <t>100% (2/2)</t>
         </is>
       </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\instacart\us\feature-usage-controller</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n"/>
@@ -1977,6 +2190,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="J43" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\instacart\us\health-controller</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n"/>
@@ -2010,6 +2228,11 @@
       <c r="I44" s="4" t="inlineStr">
         <is>
           <t>100% (26/26)</t>
+        </is>
+      </c>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\instacart\us\history-controller</t>
         </is>
       </c>
     </row>
@@ -2037,6 +2260,11 @@
       <c r="G45" s="4" t="n"/>
       <c r="H45" s="4" t="n"/>
       <c r="I45" s="4" t="n"/>
+      <c r="J45" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\instacart\us\migration-controller</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n"/>
@@ -2072,6 +2300,11 @@
           <t>100% (13/13)</t>
         </is>
       </c>
+      <c r="J46" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\instacart\us\report-controller</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n"/>
@@ -2107,6 +2340,11 @@
           <t>100% (9/9)</t>
         </is>
       </c>
+      <c r="J47" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\instacart\us\share-pass-controller</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n"/>
@@ -2142,6 +2380,11 @@
           <t>86% (19/22)</t>
         </is>
       </c>
+      <c r="J48" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\instacart\us\template-controller</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n"/>
@@ -2177,6 +2420,11 @@
           <t>100% (5/5)</t>
         </is>
       </c>
+      <c r="J49" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\instacart\us\to-event</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n"/>
@@ -2208,6 +2456,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J50" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\criteo\us\auto-task-controller</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n"/>
@@ -2243,6 +2496,11 @@
           <t>70% (7/10)</t>
         </is>
       </c>
+      <c r="J51" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\criteo\us\config-controller</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n"/>
@@ -2274,6 +2532,11 @@
           <t>0% (0/5)</t>
         </is>
       </c>
+      <c r="J52" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\criteo\us\data-impact-controller</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n"/>
@@ -2309,6 +2572,11 @@
           <t>20% (10/51)</t>
         </is>
       </c>
+      <c r="J53" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\criteo\us\definition-controller</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n"/>
@@ -2340,6 +2608,11 @@
           <t>0% (0/2)</t>
         </is>
       </c>
+      <c r="J54" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\criteo\us\feature-usage-controller</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n"/>
@@ -2371,6 +2644,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J55" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\criteo\us\health-controller</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n"/>
@@ -2404,6 +2682,11 @@
       <c r="I56" s="4" t="inlineStr">
         <is>
           <t>4% (1/26)</t>
+        </is>
+      </c>
+      <c r="J56" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\criteo\us\history-controller</t>
         </is>
       </c>
     </row>
@@ -2431,6 +2714,11 @@
       <c r="G57" s="3" t="n"/>
       <c r="H57" s="3" t="n"/>
       <c r="I57" s="3" t="n"/>
+      <c r="J57" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\criteo\us\migration-controller</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n"/>
@@ -2466,6 +2754,11 @@
           <t>23% (3/13)</t>
         </is>
       </c>
+      <c r="J58" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\criteo\us\report-controller</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n"/>
@@ -2501,6 +2794,11 @@
           <t>22% (2/9)</t>
         </is>
       </c>
+      <c r="J59" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\criteo\us\share-pass-controller</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n"/>
@@ -2536,6 +2834,11 @@
           <t>5% (1/22)</t>
         </is>
       </c>
+      <c r="J60" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\criteo\us\template-controller</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n"/>
@@ -2571,6 +2874,11 @@
           <t>20% (1/5)</t>
         </is>
       </c>
+      <c r="J61" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\criteo\us\to-event</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n"/>
@@ -2602,6 +2910,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J62" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\target\us\auto-task-controller</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n"/>
@@ -2637,6 +2950,11 @@
           <t>80% (8/10)</t>
         </is>
       </c>
+      <c r="J63" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\target\us\config-controller</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n"/>
@@ -2672,6 +2990,11 @@
           <t>40% (2/5)</t>
         </is>
       </c>
+      <c r="J64" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\target\us\data-impact-controller</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n"/>
@@ -2707,6 +3030,11 @@
           <t>37% (19/51)</t>
         </is>
       </c>
+      <c r="J65" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\target\us\definition-controller</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n"/>
@@ -2738,6 +3066,11 @@
           <t>0% (0/2)</t>
         </is>
       </c>
+      <c r="J66" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\target\us\feature-usage-controller</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n"/>
@@ -2769,6 +3102,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J67" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\target\us\health-controller</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n"/>
@@ -2802,6 +3140,11 @@
       <c r="I68" s="4" t="inlineStr">
         <is>
           <t>35% (9/26)</t>
+        </is>
+      </c>
+      <c r="J68" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\target\us\history-controller</t>
         </is>
       </c>
     </row>
@@ -2829,6 +3172,11 @@
       <c r="G69" s="3" t="n"/>
       <c r="H69" s="3" t="n"/>
       <c r="I69" s="3" t="n"/>
+      <c r="J69" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\target\us\migration-controller</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n"/>
@@ -2864,6 +3212,11 @@
           <t>100% (13/13)</t>
         </is>
       </c>
+      <c r="J70" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\target\us\report-controller</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n"/>
@@ -2899,6 +3252,11 @@
           <t>22% (2/9)</t>
         </is>
       </c>
+      <c r="J71" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\target\us\share-pass-controller</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n"/>
@@ -2934,6 +3292,11 @@
           <t>77% (17/22)</t>
         </is>
       </c>
+      <c r="J72" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\target\us\template-controller</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n"/>
@@ -2969,6 +3332,11 @@
           <t>60% (3/5)</t>
         </is>
       </c>
+      <c r="J73" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\target\us\to-event</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n"/>
@@ -3004,6 +3372,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J74" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\kroger\us\auto-task-controller</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n"/>
@@ -3039,6 +3412,11 @@
           <t>70% (7/10)</t>
         </is>
       </c>
+      <c r="J75" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\kroger\us\config-controller</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n"/>
@@ -3074,6 +3452,11 @@
           <t>0% (0/5)</t>
         </is>
       </c>
+      <c r="J76" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\kroger\us\data-impact-controller</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n"/>
@@ -3109,6 +3492,11 @@
           <t>73% (37/51)</t>
         </is>
       </c>
+      <c r="J77" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\kroger\us\definition-controller</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n"/>
@@ -3144,6 +3532,11 @@
           <t>0% (0/2)</t>
         </is>
       </c>
+      <c r="J78" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\kroger\us\feature-usage-controller</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n"/>
@@ -3179,6 +3572,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J79" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\kroger\us\health-controller</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n"/>
@@ -3212,6 +3610,11 @@
       <c r="I80" s="4" t="inlineStr">
         <is>
           <t>31% (8/26)</t>
+        </is>
+      </c>
+      <c r="J80" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\kroger\us\history-controller</t>
         </is>
       </c>
     </row>
@@ -3239,6 +3642,11 @@
       <c r="G81" s="3" t="n"/>
       <c r="H81" s="3" t="n"/>
       <c r="I81" s="3" t="n"/>
+      <c r="J81" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\kroger\us\migration-controller</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n"/>
@@ -3274,6 +3682,11 @@
           <t>8% (1/13)</t>
         </is>
       </c>
+      <c r="J82" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\kroger\us\report-controller</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n"/>
@@ -3309,6 +3722,11 @@
           <t>22% (2/9)</t>
         </is>
       </c>
+      <c r="J83" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\kroger\us\share-pass-controller</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n"/>
@@ -3344,6 +3762,11 @@
           <t>77% (17/22)</t>
         </is>
       </c>
+      <c r="J84" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\kroger\us\template-controller</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n"/>
@@ -3379,6 +3802,11 @@
           <t>40% (2/5)</t>
         </is>
       </c>
+      <c r="J85" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\kroger\us\to-event</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n"/>
@@ -3410,6 +3838,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J86" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\chewy\us\auto-task-controller</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n"/>
@@ -3445,6 +3878,11 @@
           <t>70% (7/10)</t>
         </is>
       </c>
+      <c r="J87" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\chewy\us\config-controller</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n"/>
@@ -3476,6 +3914,11 @@
           <t>0% (0/5)</t>
         </is>
       </c>
+      <c r="J88" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\chewy\us\data-impact-controller</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n"/>
@@ -3511,6 +3954,11 @@
           <t>75% (38/51)</t>
         </is>
       </c>
+      <c r="J89" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\chewy\us\definition-controller</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n"/>
@@ -3542,6 +3990,11 @@
           <t>0% (0/2)</t>
         </is>
       </c>
+      <c r="J90" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\chewy\us\feature-usage-controller</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n"/>
@@ -3573,6 +4026,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J91" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\chewy\us\health-controller</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n"/>
@@ -3606,6 +4064,11 @@
       <c r="I92" s="4" t="inlineStr">
         <is>
           <t>38% (10/26)</t>
+        </is>
+      </c>
+      <c r="J92" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\chewy\us\history-controller</t>
         </is>
       </c>
     </row>
@@ -3633,6 +4096,11 @@
       <c r="G93" s="3" t="n"/>
       <c r="H93" s="3" t="n"/>
       <c r="I93" s="3" t="n"/>
+      <c r="J93" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\chewy\us\migration-controller</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n"/>
@@ -3668,6 +4136,11 @@
           <t>8% (1/13)</t>
         </is>
       </c>
+      <c r="J94" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\chewy\us\report-controller</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n"/>
@@ -3703,6 +4176,11 @@
           <t>22% (2/9)</t>
         </is>
       </c>
+      <c r="J95" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\chewy\us\share-pass-controller</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n"/>
@@ -3738,6 +4216,11 @@
           <t>77% (17/22)</t>
         </is>
       </c>
+      <c r="J96" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\chewy\us\template-controller</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n"/>
@@ -3773,6 +4256,11 @@
           <t>40% (2/5)</t>
         </is>
       </c>
+      <c r="J97" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\chewy\us\to-event</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n"/>
@@ -3808,6 +4296,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J98" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\citrus\us\auto-task-controller</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n"/>
@@ -3843,6 +4336,11 @@
           <t>70% (7/10)</t>
         </is>
       </c>
+      <c r="J99" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\citrus\us\config-controller</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n"/>
@@ -3878,6 +4376,11 @@
           <t>40% (2/5)</t>
         </is>
       </c>
+      <c r="J100" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\citrus\us\data-impact-controller</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n"/>
@@ -3913,6 +4416,11 @@
           <t>35% (18/51)</t>
         </is>
       </c>
+      <c r="J101" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\citrus\us\definition-controller</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n"/>
@@ -3948,6 +4456,11 @@
           <t>0% (0/2)</t>
         </is>
       </c>
+      <c r="J102" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\citrus\us\feature-usage-controller</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n"/>
@@ -3983,6 +4496,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="J103" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\citrus\us\health-controller</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n"/>
@@ -4016,6 +4534,11 @@
       <c r="I104" s="4" t="inlineStr">
         <is>
           <t>62% (16/26)</t>
+        </is>
+      </c>
+      <c r="J104" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\citrus\us\history-controller</t>
         </is>
       </c>
     </row>
@@ -4043,6 +4566,11 @@
       <c r="G105" s="3" t="n"/>
       <c r="H105" s="3" t="n"/>
       <c r="I105" s="3" t="n"/>
+      <c r="J105" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\citrus\us\migration-controller</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n"/>
@@ -4078,6 +4606,11 @@
           <t>23% (3/13)</t>
         </is>
       </c>
+      <c r="J106" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\citrus\us\report-controller</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n"/>
@@ -4113,6 +4646,11 @@
           <t>22% (2/9)</t>
         </is>
       </c>
+      <c r="J107" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\citrus\us\share-pass-controller</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n"/>
@@ -4148,6 +4686,11 @@
           <t>77% (17/22)</t>
         </is>
       </c>
+      <c r="J108" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\citrus\us\template-controller</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n"/>
@@ -4183,6 +4726,11 @@
           <t>40% (2/5)</t>
         </is>
       </c>
+      <c r="J109" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\citrus\us\to-event</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n"/>
@@ -4214,6 +4762,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J110" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\doordash\us\auto-task-controller</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n"/>
@@ -4249,6 +4802,11 @@
           <t>80% (8/10)</t>
         </is>
       </c>
+      <c r="J111" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\doordash\us\config-controller</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n"/>
@@ -4284,6 +4842,11 @@
           <t>40% (2/5)</t>
         </is>
       </c>
+      <c r="J112" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\doordash\us\data-impact-controller</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n"/>
@@ -4319,6 +4882,11 @@
           <t>31% (16/51)</t>
         </is>
       </c>
+      <c r="J113" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\doordash\us\definition-controller</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n"/>
@@ -4350,6 +4918,11 @@
           <t>0% (0/2)</t>
         </is>
       </c>
+      <c r="J114" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\doordash\us\feature-usage-controller</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n"/>
@@ -4381,6 +4954,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J115" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\doordash\us\health-controller</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n"/>
@@ -4414,6 +4992,11 @@
       <c r="I116" s="4" t="inlineStr">
         <is>
           <t>54% (14/26)</t>
+        </is>
+      </c>
+      <c r="J116" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\doordash\us\history-controller</t>
         </is>
       </c>
     </row>
@@ -4441,6 +5024,11 @@
       <c r="G117" s="3" t="n"/>
       <c r="H117" s="3" t="n"/>
       <c r="I117" s="3" t="n"/>
+      <c r="J117" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\doordash\us\migration-controller</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n"/>
@@ -4476,6 +5064,11 @@
           <t>23% (3/13)</t>
         </is>
       </c>
+      <c r="J118" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\doordash\us\report-controller</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n"/>
@@ -4511,6 +5104,11 @@
           <t>22% (2/9)</t>
         </is>
       </c>
+      <c r="J119" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\doordash\us\share-pass-controller</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n"/>
@@ -4546,6 +5144,11 @@
           <t>77% (17/22)</t>
         </is>
       </c>
+      <c r="J120" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\doordash\us\template-controller</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n"/>
@@ -4581,6 +5184,11 @@
           <t>40% (2/5)</t>
         </is>
       </c>
+      <c r="J121" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\doordash\us\to-event</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n"/>
@@ -4612,6 +5220,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J122" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\samsclub\us\auto-task-controller</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n"/>
@@ -4647,6 +5260,11 @@
           <t>70% (7/10)</t>
         </is>
       </c>
+      <c r="J123" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\samsclub\us\config-controller</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n"/>
@@ -4678,6 +5296,11 @@
           <t>0% (0/5)</t>
         </is>
       </c>
+      <c r="J124" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\samsclub\us\data-impact-controller</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n"/>
@@ -4713,6 +5336,11 @@
           <t>75% (38/51)</t>
         </is>
       </c>
+      <c r="J125" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\samsclub\us\definition-controller</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n"/>
@@ -4744,6 +5372,11 @@
           <t>0% (0/2)</t>
         </is>
       </c>
+      <c r="J126" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\samsclub\us\feature-usage-controller</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n"/>
@@ -4775,6 +5408,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J127" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\samsclub\us\health-controller</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n"/>
@@ -4808,6 +5446,11 @@
       <c r="I128" s="4" t="inlineStr">
         <is>
           <t>38% (10/26)</t>
+        </is>
+      </c>
+      <c r="J128" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\samsclub\us\history-controller</t>
         </is>
       </c>
     </row>
@@ -4835,6 +5478,11 @@
       <c r="G129" s="3" t="n"/>
       <c r="H129" s="3" t="n"/>
       <c r="I129" s="3" t="n"/>
+      <c r="J129" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\samsclub\us\migration-controller</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n"/>
@@ -4870,6 +5518,11 @@
           <t>8% (1/13)</t>
         </is>
       </c>
+      <c r="J130" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\samsclub\us\report-controller</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n"/>
@@ -4905,6 +5558,11 @@
           <t>22% (2/9)</t>
         </is>
       </c>
+      <c r="J131" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\samsclub\us\share-pass-controller</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n"/>
@@ -4940,6 +5598,11 @@
           <t>77% (17/22)</t>
         </is>
       </c>
+      <c r="J132" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\samsclub\us\template-controller</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n"/>
@@ -4975,6 +5638,11 @@
           <t>40% (2/5)</t>
         </is>
       </c>
+      <c r="J133" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\samsclub\us\to-event</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n"/>
@@ -5010,6 +5678,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J134" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\bol\us\auto-task-controller</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n"/>
@@ -5045,6 +5718,11 @@
           <t>70% (7/10)</t>
         </is>
       </c>
+      <c r="J135" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\bol\us\config-controller</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n"/>
@@ -5080,6 +5758,11 @@
           <t>40% (2/5)</t>
         </is>
       </c>
+      <c r="J136" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\bol\us\data-impact-controller</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n"/>
@@ -5115,6 +5798,11 @@
           <t>29% (15/51)</t>
         </is>
       </c>
+      <c r="J137" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\bol\us\definition-controller</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n"/>
@@ -5150,6 +5838,11 @@
           <t>0% (0/2)</t>
         </is>
       </c>
+      <c r="J138" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\bol\us\feature-usage-controller</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n"/>
@@ -5185,6 +5878,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="J139" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\bol\us\health-controller</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n"/>
@@ -5218,6 +5916,11 @@
       <c r="I140" s="4" t="inlineStr">
         <is>
           <t>62% (16/26)</t>
+        </is>
+      </c>
+      <c r="J140" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\bol\us\history-controller</t>
         </is>
       </c>
     </row>
@@ -5245,6 +5948,11 @@
       <c r="G141" s="3" t="n"/>
       <c r="H141" s="3" t="n"/>
       <c r="I141" s="3" t="n"/>
+      <c r="J141" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\bol\us\migration-controller</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n"/>
@@ -5280,6 +5988,11 @@
           <t>23% (3/13)</t>
         </is>
       </c>
+      <c r="J142" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\bol\us\report-controller</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n"/>
@@ -5315,6 +6028,11 @@
           <t>22% (2/9)</t>
         </is>
       </c>
+      <c r="J143" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\bol\us\share-pass-controller</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n"/>
@@ -5350,6 +6068,11 @@
           <t>77% (17/22)</t>
         </is>
       </c>
+      <c r="J144" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\bol\us\template-controller</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n"/>
@@ -5385,6 +6108,11 @@
           <t>40% (2/5)</t>
         </is>
       </c>
+      <c r="J145" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\bol\us\to-event</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n"/>
@@ -5416,6 +6144,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J146" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\mercado\us\auto-task-controller</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n"/>
@@ -5451,6 +6184,11 @@
           <t>80% (8/10)</t>
         </is>
       </c>
+      <c r="J147" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\mercado\us\config-controller</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n"/>
@@ -5486,6 +6224,11 @@
           <t>40% (2/5)</t>
         </is>
       </c>
+      <c r="J148" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\mercado\us\data-impact-controller</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n"/>
@@ -5521,6 +6264,11 @@
           <t>12% (6/51)</t>
         </is>
       </c>
+      <c r="J149" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\mercado\us\definition-controller</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n"/>
@@ -5552,6 +6300,11 @@
           <t>0% (0/2)</t>
         </is>
       </c>
+      <c r="J150" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\mercado\us\feature-usage-controller</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n"/>
@@ -5583,6 +6336,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J151" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\mercado\us\health-controller</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n"/>
@@ -5616,6 +6374,11 @@
       <c r="I152" s="4" t="inlineStr">
         <is>
           <t>54% (14/26)</t>
+        </is>
+      </c>
+      <c r="J152" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\mercado\us\history-controller</t>
         </is>
       </c>
     </row>
@@ -5643,6 +6406,11 @@
       <c r="G153" s="3" t="n"/>
       <c r="H153" s="3" t="n"/>
       <c r="I153" s="3" t="n"/>
+      <c r="J153" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\mercado\us\migration-controller</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n"/>
@@ -5678,6 +6446,11 @@
           <t>23% (3/13)</t>
         </is>
       </c>
+      <c r="J154" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\mercado\us\report-controller</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n"/>
@@ -5713,6 +6486,11 @@
           <t>22% (2/9)</t>
         </is>
       </c>
+      <c r="J155" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\mercado\us\share-pass-controller</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n"/>
@@ -5748,6 +6526,11 @@
           <t>77% (17/22)</t>
         </is>
       </c>
+      <c r="J156" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\mercado\us\template-controller</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n"/>
@@ -5783,6 +6566,11 @@
           <t>40% (2/5)</t>
         </is>
       </c>
+      <c r="J157" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\mercado\us\to-event</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n"/>
@@ -5814,6 +6602,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J158" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\ebay\us\auto-task-controller</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n"/>
@@ -5849,6 +6642,11 @@
           <t>80% (8/10)</t>
         </is>
       </c>
+      <c r="J159" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\ebay\us\config-controller</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n"/>
@@ -5884,6 +6682,11 @@
           <t>40% (2/5)</t>
         </is>
       </c>
+      <c r="J160" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\ebay\us\data-impact-controller</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n"/>
@@ -5919,6 +6722,11 @@
           <t>35% (18/51)</t>
         </is>
       </c>
+      <c r="J161" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\ebay\us\definition-controller</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n"/>
@@ -5950,6 +6758,11 @@
           <t>0% (0/2)</t>
         </is>
       </c>
+      <c r="J162" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\ebay\us\feature-usage-controller</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="n"/>
@@ -5981,6 +6794,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J163" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\ebay\us\health-controller</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n"/>
@@ -6014,6 +6832,11 @@
       <c r="I164" s="4" t="inlineStr">
         <is>
           <t>54% (14/26)</t>
+        </is>
+      </c>
+      <c r="J164" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\ebay\us\history-controller</t>
         </is>
       </c>
     </row>
@@ -6041,6 +6864,11 @@
       <c r="G165" s="3" t="n"/>
       <c r="H165" s="3" t="n"/>
       <c r="I165" s="3" t="n"/>
+      <c r="J165" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\ebay\us\migration-controller</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n"/>
@@ -6076,6 +6904,11 @@
           <t>23% (3/13)</t>
         </is>
       </c>
+      <c r="J166" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\ebay\us\report-controller</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n"/>
@@ -6111,6 +6944,11 @@
           <t>22% (2/9)</t>
         </is>
       </c>
+      <c r="J167" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\ebay\us\share-pass-controller</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n"/>
@@ -6146,6 +6984,11 @@
           <t>77% (17/22)</t>
         </is>
       </c>
+      <c r="J168" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\ebay\us\template-controller</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n"/>
@@ -6179,6 +7022,11 @@
       <c r="I169" s="4" t="inlineStr">
         <is>
           <t>40% (2/5)</t>
+        </is>
+      </c>
+      <c r="J169" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\services\rule-api\ebay\us\to-event</t>
         </is>
       </c>
     </row>
